--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13470"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10770"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -1365,7 +1365,7 @@
     <t>Hiển thị đúng Xe đã nhập ở danh sách và popup Hiện trạng</t>
   </si>
   <si>
-    <t>30E03710</t>
+    <t>30E03933</t>
   </si>
   <si>
     <t>Minitor68_.png</t>
@@ -3803,7 +3803,7 @@
     <t>Trường "Tên khuyến mại" hiện thị: Đúng "Tên" đã nhập</t>
   </si>
   <si>
-    <t>Auto_CaiAppMoi2318</t>
+    <t>KM cài app99900</t>
   </si>
   <si>
     <t>Promotion28</t>
@@ -7143,6 +7143,9 @@
 3. Tìm kiếm &gt; Check hiển thị</t>
   </si>
   <si>
+    <t>batrinh209a</t>
+  </si>
+  <si>
     <t>Report56</t>
   </si>
   <si>
@@ -7186,9 +7189,6 @@
   <si>
     <t>Có dữ liệu tìm kiếm hàng đầu tiên
 (Hiển thị )</t>
-  </si>
-  <si>
-    <t>batrinh209a</t>
   </si>
   <si>
     <t>Report59</t>
@@ -26106,8 +26106,8 @@
     <col min="13" max="13" width="20.42578125" style="21" customWidth="1"/>
     <col min="14" max="14" width="27.140625" style="21" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="79" customWidth="1"/>
-    <col min="16" max="3152" width="9.140625" style="79" customWidth="1"/>
-    <col min="3153" max="16384" width="9.140625" style="79"/>
+    <col min="16" max="3163" width="9.140625" style="79" customWidth="1"/>
+    <col min="3164" max="16384" width="9.140625" style="79"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -41257,7 +41257,7 @@
         <v>1795</v>
       </c>
       <c r="F569" s="29" t="s">
-        <v>1748</v>
+        <v>1867</v>
       </c>
       <c r="G569" s="4" t="s">
         <v>4</v>
@@ -41274,14 +41274,14 @@
     </row>
     <row r="570" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="37" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B570" s="37" t="s">
         <v>815</v>
       </c>
       <c r="C570" s="26"/>
       <c r="D570" s="15" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="E570" s="15" t="s">
         <v>167</v>
@@ -41318,7 +41318,7 @@
     </row>
     <row r="572" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A572" s="49" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B572" s="49"/>
       <c r="C572" s="50" t="s">
@@ -41338,20 +41338,20 @@
     </row>
     <row r="573" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="37" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B573" s="39" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C573" s="26"/>
       <c r="D573" s="15" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="E573" s="27" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="F573" s="29" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="G573" s="4" t="s">
         <v>4</v>
@@ -41368,20 +41368,20 @@
     </row>
     <row r="574" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="37" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B574" s="37" t="s">
         <v>1060</v>
       </c>
       <c r="C574" s="26"/>
       <c r="D574" s="29" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="E574" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F574" s="29" t="s">
-        <v>1878</v>
+        <v>1867</v>
       </c>
       <c r="G574" s="4" t="s">
         <v>4</v>
@@ -41874,7 +41874,7 @@
         <v>1922</v>
       </c>
       <c r="E594" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F594" s="29"/>
       <c r="G594" s="4" t="s">
@@ -42000,10 +42000,10 @@
         <v>1932</v>
       </c>
       <c r="E599" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F599" s="29" t="s">
-        <v>1878</v>
+        <v>1867</v>
       </c>
       <c r="G599" s="4" t="s">
         <v>4</v>
@@ -42123,7 +42123,7 @@
         <v>1942</v>
       </c>
       <c r="E604" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F604" s="29" t="s">
         <v>1943</v>
@@ -42306,7 +42306,7 @@
         <v>1956</v>
       </c>
       <c r="E611" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F611" s="29" t="s">
         <v>1957</v>
@@ -47795,7 +47795,7 @@
         <v>2594</v>
       </c>
       <c r="E821" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F821" s="29" t="s">
         <v>2595</v>
@@ -47918,7 +47918,7 @@
         <v>2605</v>
       </c>
       <c r="E826" s="29" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F826" s="29" t="s">
         <v>2606</v>

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="2944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="2945">
   <si>
     <t>WEB STAXI - CHECKLIST AUTOMATION TEST</t>
   </si>
@@ -11160,6 +11160,9 @@
   </si>
   <si>
     <t>Tác nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đã bỏ </t>
   </si>
 </sst>
 </file>
@@ -11596,14 +11599,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11613,9 +11619,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -26127,13 +26130,13 @@
       <c r="L1" s="4"/>
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32"/>
@@ -26152,14 +26155,14 @@
       <c r="L2" s="4"/>
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
     </row>
     <row r="3" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
@@ -26181,19 +26184,19 @@
       <c r="I3" s="80"/>
       <c r="J3" s="80"/>
       <c r="K3" s="80"/>
-      <c r="L3" s="87" t="s">
+      <c r="L3" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="88"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
     </row>
     <row r="4" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32"/>
@@ -26202,7 +26205,7 @@
       </c>
       <c r="C4" s="15">
         <f>COUNTIF(H:H,"x")</f>
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D4" s="15">
         <f>COUNTIFS(G:G,"Pass",H:H,"x")</f>
@@ -26221,18 +26224,18 @@
       <c r="L4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="86" t="s">
+      <c r="M4" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="83"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
     </row>
     <row r="5" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="32"/>
@@ -26260,18 +26263,18 @@
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="82" t="s">
+      <c r="M5" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="83"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+      <c r="T5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
     </row>
     <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32"/>
@@ -26299,10 +26302,10 @@
       <c r="L6" s="6">
         <v>2</v>
       </c>
-      <c r="M6" s="82" t="s">
+      <c r="M6" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="83"/>
+      <c r="N6" s="85"/>
       <c r="O6" s="81"/>
     </row>
     <row r="7" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -26331,10 +26334,10 @@
       <c r="L7" s="6">
         <v>3</v>
       </c>
-      <c r="M7" s="82" t="s">
+      <c r="M7" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="83"/>
+      <c r="N7" s="85"/>
       <c r="O7" s="81"/>
     </row>
     <row r="8" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -27689,14 +27692,14 @@
       </c>
       <c r="F57" s="15"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="6" t="s">
-        <v>38</v>
-      </c>
+      <c r="H57" s="6"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="4"/>
-      <c r="M57" s="20"/>
+      <c r="M57" s="25" t="s">
+        <v>2944</v>
+      </c>
       <c r="N57" s="20"/>
     </row>
     <row r="58" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -15043,8 +15043,8 @@
     <col width="20.42578125" customWidth="1" style="21" min="13" max="13"/>
     <col width="27.140625" customWidth="1" style="21" min="14" max="14"/>
     <col width="14.7109375" customWidth="1" style="85" min="15" max="15"/>
-    <col width="9.140625" customWidth="1" style="85" min="16" max="3171"/>
-    <col width="9.140625" customWidth="1" style="85" min="3172" max="16384"/>
+    <col width="9.140625" customWidth="1" style="85" min="16" max="3176"/>
+    <col width="9.140625" customWidth="1" style="85" min="3177" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -15467,7 +15467,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n"/>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>Login01Login_Admin.png</t>
+        </is>
+      </c>
       <c r="N12" s="20" t="n"/>
     </row>
     <row r="13" ht="75" customHeight="1">
@@ -15522,7 +15526,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n"/>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>Login02Login_Admin.png</t>
+        </is>
+      </c>
       <c r="N13" s="20" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
@@ -15554,16 +15562,8 @@
 tài khoản: "Xin chào: [1996] Test 12/10 [1996]"</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>Xin chào: [1996] Test 12/10 [1996]</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>26/2/2026</t>
+          <t>9/3/2026</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -16295,16 +16295,8 @@
           <t>Trường "Thời điểm mất kết nối" hiển thị dữ liệu hàng đầu tiên: "Ngày hiện tại"</t>
         </is>
       </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>26/2/2026</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="4" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
@@ -16344,7 +16336,7 @@
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Đóng</t>
+          <t>Mở</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -16390,10 +16382,14 @@
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Không có dữ liệu</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n"/>
+          <t>Mở</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
@@ -16436,14 +16432,10 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Đóng</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+          <t>Không có dữ liệu</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n"/>
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
@@ -16453,7 +16445,11 @@
         </is>
       </c>
       <c r="L38" s="4" t="n"/>
-      <c r="M38" s="20" t="n"/>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>Minitor09GiamSat_TimKiem_DangVaoCaVaMatKetNoi.png</t>
+        </is>
+      </c>
       <c r="N38" s="20" t="n"/>
     </row>
     <row r="39" ht="38.45" customHeight="1">
@@ -18885,8 +18881,8 @@
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>Biển số xe: Biển số xe: 18H04971
-Thời gian: Từ ngày: 25/02/2026 20:00 Đến ngày: 26/2/2026 19:22</t>
+          <t>Biển số xe: Biển số xe: 18H02826
+Thời gian: Từ ngày: 05/03/2026 20:00 Đến ngày: 6/3/2026 8:26</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -16075,7 +16075,7 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>XEDEV113</t>
+          <t>30H99999</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>nhatnl</t>
+          <t>hoaltble</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -16628,8 +16628,8 @@
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Dữ liệu web: Đóng
-Dữ liệu excel: Mất kết nối
+          <t>Dữ liệu web: Mở
+Dữ liệu excel: Kết nối tốt
  Dòng: J6</t>
         </is>
       </c>
@@ -17009,7 +17009,11 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="20" t="inlineStr"/>
+      <c r="M55" s="20" t="inlineStr">
+        <is>
+          <t>Minitor24_GiamSatXe_CauHinhIconLoaiXe.png</t>
+        </is>
+      </c>
       <c r="N55" s="20" t="n"/>
     </row>
     <row r="56" ht="85.5" customHeight="1">
@@ -17322,7 +17326,7 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>0/64</t>
+          <t>0/63</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -17466,7 +17470,7 @@
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>64/64</t>
+          <t>63/63</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -17767,7 +17771,7 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 20.97531</t>
+          <t>Popup Hiện trạng: 20.97533</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -17891,8 +17895,8 @@
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 19:07:54
-Danh sách giám sát: 19:07:54</t>
+          <t>Popup Hiện trạng: 19:06:13
+Danh sách giám sát: 19:06:13</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -18062,7 +18066,7 @@
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 3 (TTĐH:3;App:0;Vẫy:0)</t>
+          <t>Popup Hiện trạng: 4 (TTĐH:4;App:0;Vẫy:0)</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -18102,7 +18106,7 @@
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 392000</t>
+          <t>Popup Hiện trạng: 182000</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -18409,8 +18413,18 @@
           <t>Hiển thị các trường: Thời gian, Trạng thái, Nguồn</t>
         </is>
       </c>
-      <c r="F91" s="15" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>Thời gian: 20:00:12
+Trạng thái: Sẵn sàng
+Nguồn: AppLx</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18447,7 +18461,11 @@
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18484,7 +18502,11 @@
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr"/>
-      <c r="G93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18521,7 +18543,11 @@
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18558,7 +18584,11 @@
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18595,7 +18625,11 @@
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18632,7 +18666,11 @@
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18669,8 +18707,17 @@
 2. Hiển thị: Biển số xe, thời gian</t>
         </is>
       </c>
-      <c r="F98" s="15" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>Biển số xe: Biển số xe: 17H03494
+Thời gian: Từ ngày: 16/03/2026 20:00 Đến ngày: 17/3/2026 19:6</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18706,8 +18753,16 @@
           <t>Tải file Excel chứa danh sách lộ trình xe về máy(chỉ check tải)</t>
         </is>
       </c>
-      <c r="F99" s="15" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr"/>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>_GiamSat_LoTrinh_XuatExcel.xls</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -18743,8 +18798,19 @@
           <t>Hiển thị popup các màu sắc cảnh báo: Cảnh báo, Sẵng sàng, Có khách, Nghỉ KD</t>
         </is>
       </c>
-      <c r="F100" s="15" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>Màu Vàng: Cảnh báo
+Màu đỏ: Sẵn sàng
+Màu xanh dương: Có khách
+Màu đen: Nghỉ KD</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -20322,7 +20388,7 @@
       <c r="M145" s="20" t="inlineStr"/>
       <c r="N145" s="20" t="inlineStr">
         <is>
-          <t>2024AUTO4204</t>
+          <t>2024AUTO4221</t>
         </is>
       </c>
     </row>
@@ -21468,16 +21534,8 @@
 (lái xe tạo ở ô ghi chú)</t>
         </is>
       </c>
-      <c r="F173" s="15" t="inlineStr">
-        <is>
-          <t>Thêm mới thành công</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F173" s="15" t="inlineStr"/>
+      <c r="G173" s="4" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -21685,7 +21743,7 @@
         <is>
           <t>STT: 1
 Lý do khóa: Trường test khóa xe
-Ngày khóa: 12/03/2026 19:40:41</t>
+Ngày khóa: 17/03/2026 22:09:23</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -21819,16 +21877,8 @@
           <t>Hiển thị message: "Gán xe thành công."</t>
         </is>
       </c>
-      <c r="F180" s="29" t="inlineStr">
-        <is>
-          <t>Gán xe thành công</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F180" s="29" t="inlineStr"/>
+      <c r="G180" s="4" t="inlineStr"/>
       <c r="H180" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -22541,7 +22591,7 @@
       <c r="F201" s="29" t="inlineStr">
         <is>
           <t>Tổng số ví:: 1
-Số dư ví tài khoản: 13.499.270 ₫
+Số dư ví tài khoản: 13.448.270 ₫
 Số dư ví tiền mặt: 453.200 ₫</t>
         </is>
       </c>
@@ -22779,8 +22829,8 @@
 Dịch vụ: Nạp tiền vào Ví Tài Khoản
 Số tiền: 1.000.000₫
 Nguồn tiền: Quầy thu tại hãng
-Thời gian: 19:47 - 12/03/2026
-Mã giao dịch: 10607
+Thời gian: 22:16 - 17/03/2026
+Mã giao dịch: 10747
 Nội dung: Trường test nạp tiền</t>
         </is>
       </c>
@@ -22841,8 +22891,8 @@
 Số tiền: 100 VNĐ
 Dịch vụ: Rút tiền Ví Tiền Mặt
 Nguồn : Rút tại quầy
-Thời gian: 19:47 - 12/03/2026
-Mã giao dịch: 10608
+Thời gian: 22:16 - 17/03/2026
+Mã giao dịch: 10748
 Nội dung: Trường test rút tiền</t>
         </is>
       </c>
@@ -23618,7 +23668,11 @@
       <c r="J227" s="2" t="n"/>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="n"/>
-      <c r="M227" s="42" t="inlineStr"/>
+      <c r="M227" s="42" t="inlineStr">
+        <is>
+          <t>Wallet22_XacNhanGiaoDich_DongYXacNhan.png</t>
+        </is>
+      </c>
       <c r="N227" s="42" t="n"/>
     </row>
     <row r="228" ht="56.45" customHeight="1">
@@ -24317,7 +24371,7 @@
       <c r="F245" s="29" t="inlineStr">
         <is>
           <t>Chuyển tới trang: 8.4 Báo cáo doanh thu
-Mã quốc khách: 0011F1F5</t>
+Mã quốc khách: 0011F2BD</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -24584,16 +24638,8 @@
           <t>Trường "Tên khuyến mại" hiện thị "Tên khuyến mại "giống với dữ liệu đã nhập"</t>
         </is>
       </c>
-      <c r="F253" s="29" t="inlineStr">
-        <is>
-          <t>KM 8/3</t>
-        </is>
-      </c>
-      <c r="G253" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F253" s="29" t="inlineStr"/>
+      <c r="G253" s="4" t="inlineStr"/>
       <c r="H253" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -25306,7 +25352,7 @@
       </c>
       <c r="F270" s="29" t="inlineStr">
         <is>
-          <t>03596674206</t>
+          <t>03596674223</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -25566,7 +25612,7 @@
       <c r="M275" s="42" t="inlineStr"/>
       <c r="N275" s="42" t="inlineStr">
         <is>
-          <t>2100004208</t>
+          <t>2100004225</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25672,7 @@
       <c r="M276" s="42" t="inlineStr"/>
       <c r="N276" s="42" t="inlineStr">
         <is>
-          <t>2100004209</t>
+          <t>2100004226</t>
         </is>
       </c>
     </row>
@@ -25868,12 +25914,12 @@
       </c>
       <c r="F283" s="29" t="inlineStr">
         <is>
-          <t>Km cài app mới 2</t>
+          <t>Km cài app mới 4</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
@@ -25885,11 +25931,7 @@
       <c r="J283" s="2" t="n"/>
       <c r="K283" s="2" t="n"/>
       <c r="L283" s="2" t="n"/>
-      <c r="M283" s="42" t="inlineStr">
-        <is>
-          <t>Promotion27_CaiAppMoi_TimKiem.png</t>
-        </is>
-      </c>
+      <c r="M283" s="42" t="inlineStr"/>
       <c r="N283" s="42" t="n"/>
     </row>
     <row r="284" ht="43.5" customHeight="1">
@@ -26693,7 +26735,7 @@
       </c>
       <c r="F307" s="29" t="inlineStr">
         <is>
-          <t>Km 30k</t>
+          <t>Km cài app mới 2</t>
         </is>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -28145,7 +28187,7 @@
       </c>
       <c r="F351" s="29" t="inlineStr">
         <is>
-          <t>Trường</t>
+          <t>tr</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -29424,7 +29466,7 @@
       <c r="M384" s="42" t="inlineStr"/>
       <c r="N384" s="42" t="inlineStr">
         <is>
-          <t>Auto4211</t>
+          <t>Auto4228</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29839,7 @@
       </c>
       <c r="F394" s="29" t="inlineStr">
         <is>
-          <t>Auto_4203</t>
+          <t>Auto_4219</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -30346,7 +30388,7 @@
       <c r="M407" s="42" t="inlineStr"/>
       <c r="N407" s="42" t="inlineStr">
         <is>
-          <t>Auto_4212</t>
+          <t>Auto_4229</t>
         </is>
       </c>
     </row>
@@ -30750,16 +30792,8 @@
 </t>
         </is>
       </c>
-      <c r="F416" s="29" t="inlineStr">
-        <is>
-          <t>Cập nhật thông tin thẻ thành công</t>
-        </is>
-      </c>
-      <c r="G416" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F416" s="29" t="inlineStr"/>
+      <c r="G416" s="4" t="inlineStr"/>
       <c r="H416" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -33077,7 +33111,7 @@
       </c>
       <c r="F477" s="29" t="inlineStr">
         <is>
-          <t>00118001</t>
+          <t>001180B9</t>
         </is>
       </c>
       <c r="G477" s="4" t="inlineStr">
@@ -33166,14 +33200,10 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F479" s="29" t="inlineStr">
-        <is>
-          <t>_BaoCaoCuocKhachTong_ExcelFull.xlsx</t>
-        </is>
-      </c>
+      <c r="F479" s="29" t="inlineStr"/>
       <c r="G479" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H479" s="6" t="inlineStr">
@@ -33185,7 +33215,11 @@
       <c r="J479" s="2" t="n"/>
       <c r="K479" s="2" t="n"/>
       <c r="L479" s="2" t="n"/>
-      <c r="M479" s="42" t="inlineStr"/>
+      <c r="M479" s="42" t="inlineStr">
+        <is>
+          <t>Report04_BaoCaoCuocKhachTong_XuatExcelDayDuThongTin.png</t>
+        </is>
+      </c>
       <c r="N479" s="42" t="n"/>
     </row>
     <row r="480">
@@ -33415,30 +33449,54 @@
       </c>
       <c r="F486" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">None, 36/43
-, None, 14/14
-, None, 0/0
-, None, 22/22
-, None, 0/0
-, None, 0/0
-, None, 0/0
-, None, 1/4
-, None, 2/2
-, None, 1/1
-, None, 32/39
-, None, 0/0
-, None, 36/43
-, None, 14/14
-, None, 0/0
-, None, 22/22
-, None, 0/0
-, None, 0/0
-, None, 0/0
-, None, 1/4
-, None, 2/2
-, None, 1/1
-, None, 32/39
-, None, 0/0
+          <t xml:space="preserve">Tổng cuốc_x000D_
+(1), 60/68
+, Nguồn mobile_x000D_
+(3), 15/15
+, Nguồn điều hành_x000D_
+(5), 5/5
+, Nguồn vãng lai_x000D_
+(6), 40/40
+, Nguồn khách vẫy_x000D_
+(7), 0/0
+, Nguồn Đồng hồ metter_x000D_
+(8), 0/0
+, Nguồn đối tác_x000D_
+(9), 0/0
+, Tổng không đề cử_x000D_
+(11), 1/2
+, Tổng khách hủy_x000D_
+(12), 0/0
+, Tổng lái xe hủy_x000D_
+(13), 1/1
+, Tổng thành công_x000D_
+(14), 54/62
+, Không có lái xe nhận_x000D_
+(15), 4/4
+, Tổng cuốc_x000D_
+(1), 60/68
+, Nguồn mobile_x000D_
+(3), 15/15
+, Nguồn điều hành_x000D_
+(5), 5/5
+, Nguồn vãng lai_x000D_
+(6), 40/40
+, Nguồn khách vẫy_x000D_
+(7), 0/0
+, Nguồn Đồng hồ metter_x000D_
+(8), 0/0
+, Nguồn đối tác_x000D_
+(9), 0/0
+, Tổng không đề cử_x000D_
+(11), 1/2
+, Tổng khách hủy_x000D_
+(12), 0/0
+, Tổng lái xe hủy_x000D_
+(13), 1/1
+, Tổng thành công_x000D_
+(14), 54/62
+, Không có lái xe nhận_x000D_
+(15), 4/4
 </t>
         </is>
       </c>
@@ -33489,18 +33547,30 @@
       </c>
       <c r="F487" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">None, 21/21
-, None, 10/10
-, None, 1/1
-, None, 9/9
-, None, 0/0
-, None, 0/0
-, None, 0/0
-, None, 3/3
-, None, 4/4
-, None, 0/0
-, None, 14/14
-, None, 0/0
+          <t xml:space="preserve">Tổng cuốc_x000D_
+(1), 0/0
+, Nguồn mobile_x000D_
+(3), 0/0
+, Nguồn điều hành_x000D_
+(5), 0/0
+, Nguồn vãng lai_x000D_
+(6), 0/0
+, Nguồn khách vẫy_x000D_
+(7), 0/0
+, Nguồn Đồng hồ metter_x000D_
+(8), 0/0
+, Nguồn đối tác_x000D_
+(9), 0/0
+, Tổng không đề cử_x000D_
+(11), 0/0
+, Tổng khách hủy_x000D_
+(12), 0/0
+, Tổng lái xe hủy_x000D_
+(13), 0/0
+, Tổng thành công_x000D_
+(14), 0/0
+, Không có lái xe nhận_x000D_
+(15), 0/0
 </t>
         </is>
       </c>
@@ -35797,7 +35867,7 @@
       </c>
       <c r="F558" s="29" t="inlineStr">
         <is>
-          <t>Vương Văn Thuận</t>
+          <t>Bui Văn Du</t>
         </is>
       </c>
       <c r="G558" s="4" t="inlineStr">
@@ -35841,14 +35911,10 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F559" s="29" t="inlineStr">
-        <is>
-          <t>_BaoCaoDoanhThuTheoLaiXe.xlsx</t>
-        </is>
-      </c>
+      <c r="F559" s="29" t="inlineStr"/>
       <c r="G559" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H559" s="6" t="inlineStr">
@@ -35860,7 +35926,11 @@
       <c r="J559" s="2" t="n"/>
       <c r="K559" s="2" t="n"/>
       <c r="L559" s="2" t="n"/>
-      <c r="M559" s="42" t="inlineStr"/>
+      <c r="M559" s="42" t="inlineStr">
+        <is>
+          <t>Report49_BaoCaoDoanhThuTheoLaiXe_XuatExcel.png</t>
+        </is>
+      </c>
       <c r="N559" s="42" t="n"/>
     </row>
     <row r="560">
@@ -35982,7 +36052,7 @@
       </c>
       <c r="F563" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Taxi thông thường</t>
         </is>
       </c>
       <c r="G563" s="4" t="inlineStr">
@@ -36026,14 +36096,10 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F564" s="26" t="inlineStr">
-        <is>
-          <t>_ChiTietDoanhThuTuApp.xlsx</t>
-        </is>
-      </c>
+      <c r="F564" s="26" t="inlineStr"/>
       <c r="G564" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H564" s="6" t="inlineStr">
@@ -36045,7 +36111,11 @@
       <c r="J564" s="2" t="n"/>
       <c r="K564" s="2" t="n"/>
       <c r="L564" s="2" t="n"/>
-      <c r="M564" s="42" t="inlineStr"/>
+      <c r="M564" s="42" t="inlineStr">
+        <is>
+          <t>Report52_ChiTietDoanhThuTuApp_XuatExcel.png</t>
+        </is>
+      </c>
       <c r="N564" s="42" t="n"/>
     </row>
     <row r="565" ht="75" customHeight="1">
@@ -36072,14 +36142,10 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F565" s="29" t="inlineStr">
-        <is>
-          <t>_ChiTietDoanhThuTuApp_Full.xlsx</t>
-        </is>
-      </c>
+      <c r="F565" s="29" t="inlineStr"/>
       <c r="G565" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H565" s="6" t="inlineStr">
@@ -36091,7 +36157,11 @@
       <c r="J565" s="2" t="n"/>
       <c r="K565" s="2" t="n"/>
       <c r="L565" s="2" t="n"/>
-      <c r="M565" s="42" t="inlineStr"/>
+      <c r="M565" s="42" t="inlineStr">
+        <is>
+          <t>Report53_ChiTietDoanhThuTuApp_XuatExcelFull.png</t>
+        </is>
+      </c>
       <c r="N565" s="42" t="n"/>
     </row>
     <row r="566">
@@ -39463,16 +39533,8 @@
           <t>Chuyển đến trang: "10.3.8 Danh sách cấu hình Webpage"</t>
         </is>
       </c>
-      <c r="F667" s="29" t="inlineStr">
-        <is>
-          <t>10.3.8 Danh sách cấu hình Webpage</t>
-        </is>
-      </c>
-      <c r="G667" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F667" s="29" t="inlineStr"/>
+      <c r="G667" s="4" t="inlineStr"/>
       <c r="H667" s="2" t="n"/>
       <c r="I667" s="2" t="n"/>
       <c r="J667" s="2" t="n"/>
@@ -39506,16 +39568,8 @@
           <t>Trường "Tiêu đề" hiển thị dữ liệu đã nhập</t>
         </is>
       </c>
-      <c r="F668" s="29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G668" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F668" s="29" t="inlineStr"/>
+      <c r="G668" s="4" t="inlineStr"/>
       <c r="H668" s="2" t="n"/>
       <c r="I668" s="2" t="n"/>
       <c r="J668" s="2" t="n"/>
@@ -39549,16 +39603,8 @@
           <t>Trường "Code" hiển thị dữ liệu đã nhập</t>
         </is>
       </c>
-      <c r="F669" s="29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G669" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F669" s="29" t="inlineStr"/>
+      <c r="G669" s="4" t="inlineStr"/>
       <c r="H669" s="2" t="n"/>
       <c r="I669" s="2" t="n"/>
       <c r="J669" s="2" t="n"/>
@@ -39591,16 +39637,8 @@
           <t>Hiển thị message: "Lưu thông tin thành công."</t>
         </is>
       </c>
-      <c r="F670" s="29" t="inlineStr">
-        <is>
-          <t>Thêm mới cấu hình thành công!</t>
-        </is>
-      </c>
-      <c r="G670" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F670" s="29" t="inlineStr"/>
+      <c r="G670" s="4" t="inlineStr"/>
       <c r="H670" s="2" t="n"/>
       <c r="I670" s="2" t="n"/>
       <c r="J670" s="2" t="n"/>
@@ -39633,16 +39671,8 @@
           <t>Hiển thị message: "Lưu thông tin thành công."</t>
         </is>
       </c>
-      <c r="F671" s="29" t="inlineStr">
-        <is>
-          <t>Cập nhật thay đổi thành công!</t>
-        </is>
-      </c>
-      <c r="G671" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F671" s="29" t="inlineStr"/>
+      <c r="G671" s="4" t="inlineStr"/>
       <c r="H671" s="2" t="n"/>
       <c r="I671" s="2" t="n"/>
       <c r="J671" s="2" t="n"/>
@@ -39675,26 +39705,14 @@
           <t>Hiển thị message: "Lưu thông tin thành công."</t>
         </is>
       </c>
-      <c r="F672" s="29" t="inlineStr">
-        <is>
-          <t>Thêm mới cấu hình thành công!</t>
-        </is>
-      </c>
-      <c r="G672" s="4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
+      <c r="F672" s="29" t="inlineStr"/>
+      <c r="G672" s="4" t="inlineStr"/>
       <c r="H672" s="2" t="n"/>
       <c r="I672" s="2" t="n"/>
       <c r="J672" s="2" t="n"/>
       <c r="K672" s="2" t="n"/>
       <c r="L672" s="2" t="n"/>
-      <c r="M672" s="42" t="inlineStr">
-        <is>
-          <t>Admin20_6_CHwebpage_ThemMoi.png</t>
-        </is>
-      </c>
+      <c r="M672" s="42" t="inlineStr"/>
       <c r="N672" s="42" t="n"/>
     </row>
     <row r="673" ht="75" customHeight="1">
@@ -39721,16 +39739,8 @@
           <t>Hiển thị message: "Xóa thông tin thành công"</t>
         </is>
       </c>
-      <c r="F673" s="29" t="inlineStr">
-        <is>
-          <t>Xóa cấu hình thành công!</t>
-        </is>
-      </c>
-      <c r="G673" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F673" s="29" t="inlineStr"/>
+      <c r="G673" s="4" t="inlineStr"/>
       <c r="H673" s="2" t="n"/>
       <c r="I673" s="2" t="n"/>
       <c r="J673" s="2" t="n"/>
@@ -40304,7 +40314,7 @@
       <c r="M690" s="42" t="inlineStr"/>
       <c r="N690" s="42" t="inlineStr">
         <is>
-          <t>auto4216</t>
+          <t>auto4233</t>
         </is>
       </c>
     </row>
@@ -41283,12 +41293,12 @@
       </c>
       <c r="F716" s="29" t="inlineStr">
         <is>
-          <t>STT: 1
+          <t xml:space="preserve">STT: 1
 Tên cấu hình: ZOOM_MAP
 Giá trị: {"android": 18, "iOS": 18, "minDistanceToMove": 15}
 Kiểu dữ liệu: Kiểu chuỗi
 Công ty: Cấu hình zoom mặc đinh ở màn hình home (Chỉ áp dụng cho app xamarin)
-Ghi chú: Hãng quản lý</t>
+Ghi chú: </t>
         </is>
       </c>
       <c r="G716" s="4" t="inlineStr">
@@ -42507,7 +42517,7 @@
       </c>
       <c r="F756" s="29" t="inlineStr">
         <is>
-          <t>Cộng ví tiền mặt khi hoàn thành chuyến thanh toán thẻ. Số dư tài khoản: 1206000đ</t>
+          <t>Cộng ví tiền mặt khi hoàn thành chuyến thanh toán thẻ. Số dư tài khoản: 176000đ</t>
         </is>
       </c>
       <c r="G756" s="4" t="inlineStr">
@@ -43126,7 +43136,7 @@
       <c r="M771" s="42" t="inlineStr"/>
       <c r="N771" s="67" t="inlineStr">
         <is>
-          <t>Auto_ThongBao_4217</t>
+          <t>Auto_ThongBao_4220</t>
         </is>
       </c>
     </row>
@@ -43463,7 +43473,7 @@
       </c>
       <c r="F780" s="29" t="inlineStr">
         <is>
-          <t>Ví tài khoản: -4.600đ, hoàn thành cuốc</t>
+          <t>Ví tài khoản: -20.000đ, hoàn thành cuốc</t>
         </is>
       </c>
       <c r="G780" s="4" t="inlineStr">

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -16073,16 +16073,8 @@
           <t>Trường "Biển số" hiển thị dữ liệu hàng đầu tiên: "Biển số vừa nhập"</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>BATONNT</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F31" s="15" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -16158,16 +16150,8 @@
           <t>Trường "Đang lái" hiển thị dữ liệu hàng đầu tiên: "0945912674"</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>batonnt</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F33" s="15" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -17009,11 +16993,7 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="20" t="inlineStr">
-        <is>
-          <t>Minitor24_GiamSatXe_CauHinhIconLoaiXe.png</t>
-        </is>
-      </c>
+      <c r="M55" s="20" t="inlineStr"/>
       <c r="N55" s="20" t="n"/>
     </row>
     <row r="56" ht="85.5" customHeight="1">
@@ -17326,7 +17306,7 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>0/61</t>
+          <t>0/63</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -17374,7 +17354,7 @@
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>https://app.staxi.vn/Content/themes/img/WarGreenCar.png</t>
+          <t>https://app.staxi.vn/Content/themes/img/RedCar.png</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -17470,7 +17450,7 @@
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>61/61</t>
+          <t>63/63</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -17690,7 +17670,7 @@
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 15A26611</t>
+          <t>Popup Hiện trạng: 15A32281</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -17730,8 +17710,8 @@
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 202
-Danh sách giám sát: 202</t>
+          <t>Popup Hiện trạng: 219
+Danh sách giám sát: 219</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -17771,7 +17751,7 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 20.92529</t>
+          <t>Popup Hiện trạng: 20.79097</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -17811,7 +17791,7 @@
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 106.6611</t>
+          <t>Popup Hiện trạng: 106.66</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -17851,7 +17831,7 @@
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: P. Thủy Nguyên, TP. Hải Phòng</t>
+          <t>Popup Hiện trạng: 721, Mạc Đăng Doanh, P. Hưng Đạo, TP. Hải Phòng</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -17895,8 +17875,8 @@
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 21:35:21
-Danh sách giám sát: 21:35:21</t>
+          <t>Popup Hiện trạng: 06:47:10
+Danh sách giám sát: 06:47:10</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -18066,7 +18046,7 @@
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 3 (TTĐH:3;App:0;Vẫy:0)</t>
+          <t>Popup Hiện trạng: 0 (TTĐH:0;App:0;Vẫy:0)</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -18106,7 +18086,7 @@
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 330000</t>
+          <t>Popup Hiện trạng: 0</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -18146,7 +18126,7 @@
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: VŨ LONG AN</t>
+          <t>Popup Hiện trạng: BÙI TIẾN KIẾM</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -18186,7 +18166,7 @@
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 0866692456</t>
+          <t>Popup Hiện trạng: 0948317256</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -18266,7 +18246,7 @@
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 609090</t>
+          <t>Popup Hiện trạng: 611030</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -18413,16 +18393,10 @@
           <t>Hiển thị các trường: Thời gian, Trạng thái, Nguồn</t>
         </is>
       </c>
-      <c r="F91" s="15" t="inlineStr">
-        <is>
-          <t>Thời gian: 04:51:19
-Trạng thái: Nghỉ KD
-Nguồn: AppLx</t>
-        </is>
-      </c>
+      <c r="F91" s="15" t="inlineStr"/>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -18713,8 +18687,8 @@
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>Biển số xe: Biển số xe: 18H06220
-Thời gian: Từ ngày: 25/03/2026 20:00 Đến ngày: 26/3/2026 21:38</t>
+          <t>Biển số xe: Biển số xe: 18H06258
+Thời gian: Từ ngày: 01/04/2026 20:00 Đến ngày: 1/4/2026 6:58</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -19304,7 +19278,7 @@
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 21:41:17 26/03/26</t>
+          <t>Popup Hiện trạng: 07:01:37 01/04/26</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -19344,7 +19318,7 @@
       </c>
       <c r="F115" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 21.05851</t>
+          <t>Popup Hiện trạng: 21.01807</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -19384,7 +19358,7 @@
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 105.7832</t>
+          <t>Popup Hiện trạng: 105.8504</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -19424,7 +19398,7 @@
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 507, Phạm Văn Đồng, P. Xuân Đỉnh, TP. Hà Nội</t>
+          <t>Popup Hiện trạng: 14, Triệu Việt Vương, P. Hai Bà Trưng, TP. Hà Nội</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -19464,7 +19438,7 @@
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 10</t>
+          <t>Popup Hiện trạng: 0</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -19504,7 +19478,7 @@
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: Đào Văn Sáu</t>
+          <t>Popup Hiện trạng: Đào Văn Việt</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -19544,7 +19518,7 @@
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 0985619905</t>
+          <t>Popup Hiện trạng: 0983942739</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -19624,7 +19598,7 @@
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>Popup Hiện trạng: 3 (TTĐH: 3; App: 0; Vẫy: 0)</t>
+          <t>Popup Hiện trạng: 2 (TTĐH: 2; App: 0; Vẫy: 0)</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -19859,7 +19833,7 @@
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>30E68089</t>
+          <t>30E68063</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -19906,7 +19880,7 @@
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -20531,7 +20505,7 @@
       <c r="M145" s="20" t="inlineStr"/>
       <c r="N145" s="20" t="inlineStr">
         <is>
-          <t>2024AUTO4334</t>
+          <t>2024AUTO4415</t>
         </is>
       </c>
     </row>
@@ -21215,7 +21189,7 @@
       </c>
       <c r="F162" s="29" t="inlineStr">
         <is>
-          <t>XE24656</t>
+          <t>30K73737</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -21340,7 +21314,7 @@
       </c>
       <c r="F165" s="29" t="inlineStr">
         <is>
-          <t>0967303024</t>
+          <t>0984368814</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -21537,14 +21511,10 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F170" s="15" t="inlineStr">
-        <is>
-          <t>_laixe.xls</t>
-        </is>
-      </c>
+      <c r="F170" s="15" t="inlineStr"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
@@ -21555,7 +21525,11 @@
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="6" t="n"/>
       <c r="L170" s="4" t="n"/>
-      <c r="M170" s="20" t="inlineStr"/>
+      <c r="M170" s="20" t="inlineStr">
+        <is>
+          <t>Vehicle42_LaiXe_TaiExcel.png</t>
+        </is>
+      </c>
       <c r="N170" s="20" t="n"/>
     </row>
     <row r="171" ht="75" customHeight="1">
@@ -21703,7 +21677,7 @@
       <c r="M173" s="20" t="inlineStr"/>
       <c r="N173" s="20" t="inlineStr">
         <is>
-          <t>auto4335</t>
+          <t>auto4416</t>
         </is>
       </c>
     </row>
@@ -21797,8 +21771,16 @@
           <t>Hiển thị message: "Cập nhật lái xe thành công"</t>
         </is>
       </c>
-      <c r="F175" s="29" t="inlineStr"/>
-      <c r="G175" s="4" t="inlineStr"/>
+      <c r="F175" s="29" t="inlineStr">
+        <is>
+          <t>Cập nhật thành công</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -21886,7 +21868,7 @@
         <is>
           <t>STT: 1
 Lý do khóa: Trường test khóa xe
-Ngày khóa: 26/03/2026 21:55:41</t>
+Ngày khóa: 01/04/2026 07:15:49</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -22742,8 +22724,8 @@
       <c r="F201" s="29" t="inlineStr">
         <is>
           <t>Tổng số ví:: 1
-Số dư ví tài khoản: 13.193.270 ₫
-Số dư ví tiền mặt: 453.100 ₫</t>
+Số dư ví tài khoản: 53.881.000 ₫
+Số dư ví tiền mặt: 585.300 ₫</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -22790,7 +22772,7 @@
       </c>
       <c r="F202" s="29" t="inlineStr">
         <is>
-          <t>Phan Văn Khuyên</t>
+          <t>Nguyễn Văn Tài 90</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -22837,7 +22819,7 @@
       </c>
       <c r="F203" s="29" t="inlineStr">
         <is>
-          <t>0335735161</t>
+          <t>auto376</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -22972,24 +22954,8 @@
 - Nội dung: Trường test nạp tiền</t>
         </is>
       </c>
-      <c r="F206" s="29" t="inlineStr">
-        <is>
-          <t>Message: Đã lưu lại giao dịch, Chờ xác nhận.
-Số tiền: 1.000.000 VNĐ
-Tên ví: batonnt1
-Dịch vụ: Nạp tiền vào Ví Tài Khoản
-Số tiền: 1.000.000₫
-Nguồn tiền: Quầy thu tại hãng
-Thời gian: 22:03 - 26/03/2026
-Mã giao dịch: 10929
-Nội dung: Trường test nạp tiền</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F206" s="29" t="inlineStr"/>
+      <c r="G206" s="4" t="inlineStr"/>
       <c r="H206" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -23042,8 +23008,8 @@
 Số tiền: 100 VNĐ
 Dịch vụ: Rút tiền Ví Tiền Mặt
 Nguồn : Rút tại quầy
-Thời gian: 22:03 - 26/03/2026
-Mã giao dịch: 10930
+Thời gian: 07:22 - 01/04/2026
+Mã giao dịch: 2807
 Nội dung: Trường test rút tiền</t>
         </is>
       </c>
@@ -23627,7 +23593,7 @@
       </c>
       <c r="F223" s="29" t="inlineStr">
         <is>
-          <t>0837393453</t>
+          <t>0123666666</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -24021,8 +23987,16 @@
           <t>Trường "Tên lái xe" hiện thị đúng với "Tên lái xe" đã nhập</t>
         </is>
       </c>
-      <c r="F233" s="29" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr"/>
+      <c r="F233" s="29" t="inlineStr">
+        <is>
+          <t>batonnt1</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -24510,7 +24484,7 @@
       <c r="F245" s="29" t="inlineStr">
         <is>
           <t>Chuyển tới trang: 8.4 Báo cáo doanh thu
-Mã quốc khách: 0011F3AD</t>
+Mã quốc khách: 00AEC636</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -24779,7 +24753,7 @@
       </c>
       <c r="F253" s="29" t="inlineStr">
         <is>
-          <t>KM1111</t>
+          <t>Auto_KM_Rieng4021</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
@@ -25499,7 +25473,7 @@
       </c>
       <c r="F270" s="29" t="inlineStr">
         <is>
-          <t>03596674336</t>
+          <t>2100004391</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -25759,7 +25733,7 @@
       <c r="M275" s="42" t="inlineStr"/>
       <c r="N275" s="42" t="inlineStr">
         <is>
-          <t>2100004338</t>
+          <t>2100004419</t>
         </is>
       </c>
     </row>
@@ -25819,7 +25793,7 @@
       <c r="M276" s="42" t="inlineStr"/>
       <c r="N276" s="42" t="inlineStr">
         <is>
-          <t>2100004339</t>
+          <t>2100004420</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26035,7 @@
       </c>
       <c r="F283" s="29" t="inlineStr">
         <is>
-          <t>KM cài app 899</t>
+          <t>Auto_CaiAppMoi4331</t>
         </is>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -26393,8 +26367,16 @@
           <t>Hiển thị dữ liệu trong khoảng Từ ngày Đến ngày và hiển thị các trường: STT, Công ty, Mã KM, Tên KM, Phải thu, Phải trả, Chi tiết.</t>
         </is>
       </c>
-      <c r="F292" s="29" t="inlineStr"/>
-      <c r="G292" s="4" t="inlineStr"/>
+      <c r="F292" s="29" t="inlineStr">
+        <is>
+          <t>G7 Taxi Hà Nội</t>
+        </is>
+      </c>
+      <c r="G292" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H292" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -26872,8 +26854,16 @@
           <t>Hiển thị dữ liệu trong khoảng Từ ngày Đến ngày và hiển thị các trường: STT, Tên khuyến mại, Tổng tiền đã khuyến mại, Tổng số khuyến mại đã sử dụng, Tháng/Năm.</t>
         </is>
       </c>
-      <c r="F307" s="29" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr"/>
+      <c r="F307" s="29" t="inlineStr">
+        <is>
+          <t>KM 30%</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H307" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -27884,7 +27874,7 @@
       <c r="M338" s="42" t="inlineStr"/>
       <c r="N338" s="42" t="inlineStr">
         <is>
-          <t>Auto_account_4307</t>
+          <t>Auto_account_4350</t>
         </is>
       </c>
     </row>
@@ -28096,7 +28086,7 @@
       <c r="M344" s="42" t="inlineStr"/>
       <c r="N344" s="42" t="inlineStr">
         <is>
-          <t>Auto_group_4308</t>
+          <t>Auto_group_4351</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28308,7 @@
       </c>
       <c r="F351" s="29" t="inlineStr">
         <is>
-          <t>tr</t>
+          <t>Auto_customer_4309</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -28585,7 +28575,7 @@
       <c r="M357" s="42" t="inlineStr"/>
       <c r="N357" s="42" t="inlineStr">
         <is>
-          <t>Auto_customer_4309</t>
+          <t>Auto_customer_4352</t>
         </is>
       </c>
     </row>
@@ -29050,7 +29040,7 @@
       </c>
       <c r="F371" s="29" t="inlineStr">
         <is>
-          <t>TUSINHTUAPP</t>
+          <t>DOI TAC MAC DINH</t>
         </is>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -29193,7 +29183,7 @@
       <c r="M374" s="42" t="inlineStr"/>
       <c r="N374" s="42" t="inlineStr">
         <is>
-          <t>Auto_name_partner_4310</t>
+          <t>Auto_name_partner_4353</t>
         </is>
       </c>
     </row>
@@ -29393,7 +29383,7 @@
       </c>
       <c r="F380" s="29" t="inlineStr">
         <is>
-          <t>THAODTP3333</t>
+          <t>SEC0027</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
@@ -29597,7 +29587,7 @@
       <c r="M384" s="42" t="inlineStr"/>
       <c r="N384" s="42" t="inlineStr">
         <is>
-          <t>Auto4341</t>
+          <t>Auto4422</t>
         </is>
       </c>
     </row>
@@ -29882,7 +29872,7 @@
       </c>
       <c r="F392" s="29" t="inlineStr">
         <is>
-          <t>0999999998</t>
+          <t>0984075597</t>
         </is>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -29970,7 +29960,7 @@
       </c>
       <c r="F394" s="29" t="inlineStr">
         <is>
-          <t>BATHAO1</t>
+          <t>Auto_4411</t>
         </is>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -30519,7 +30509,7 @@
       <c r="M407" s="42" t="inlineStr"/>
       <c r="N407" s="42" t="inlineStr">
         <is>
-          <t>Auto_4342</t>
+          <t>Auto_4423</t>
         </is>
       </c>
     </row>
@@ -30945,7 +30935,7 @@
       <c r="M416" s="42" t="inlineStr"/>
       <c r="N416" s="42" t="inlineStr">
         <is>
-          <t>Auto_4344</t>
+          <t>Auto_4425</t>
         </is>
       </c>
     </row>
@@ -31118,7 +31108,7 @@
       <c r="M420" s="42" t="inlineStr"/>
       <c r="N420" s="42" t="inlineStr">
         <is>
-          <t>5527854570069252</t>
+          <t>5527854570069253</t>
         </is>
       </c>
     </row>
@@ -32036,7 +32026,7 @@
       </c>
       <c r="F447" s="29" t="inlineStr">
         <is>
-          <t>9999209984075597</t>
+          <t>8880999016579311</t>
         </is>
       </c>
       <c r="G447" s="4" t="inlineStr">
@@ -32081,7 +32071,13 @@
 (Xem file log)</t>
         </is>
       </c>
-      <c r="F448" s="29" t="inlineStr"/>
+      <c r="F448" s="29" t="inlineStr">
+        <is>
+          <t>Dữ liệu web: -
+Dữ liệu excel: None
+ Dòng: L6</t>
+        </is>
+      </c>
       <c r="G448" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
@@ -32122,14 +32118,10 @@
           <t>Hiện thị thông báo: "Cập nhật thành công!"</t>
         </is>
       </c>
-      <c r="F449" s="29" t="inlineStr">
-        <is>
-          <t>Cập nhật thành công!</t>
-        </is>
-      </c>
+      <c r="F449" s="29" t="inlineStr"/>
       <c r="G449" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H449" s="6" t="inlineStr">
@@ -33254,7 +33246,7 @@
       </c>
       <c r="F477" s="29" t="inlineStr">
         <is>
-          <t>001180B9</t>
+          <t>00AEC0BC</t>
         </is>
       </c>
       <c r="G477" s="4" t="inlineStr">
@@ -33303,7 +33295,7 @@
       <c r="F478" s="29" t="inlineStr"/>
       <c r="G478" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H478" s="6" t="inlineStr">
@@ -33343,10 +33335,14 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F479" s="29" t="inlineStr"/>
+      <c r="F479" s="29" t="inlineStr">
+        <is>
+          <t>_BaoCaoCuocKhachTong_ExcelFull.xlsx</t>
+        </is>
+      </c>
       <c r="G479" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H479" s="6" t="inlineStr">
@@ -33358,11 +33354,7 @@
       <c r="J479" s="2" t="n"/>
       <c r="K479" s="2" t="n"/>
       <c r="L479" s="2" t="n"/>
-      <c r="M479" s="42" t="inlineStr">
-        <is>
-          <t>Report04_BaoCaoCuocKhachTong_XuatExcelDayDuThongTin.png</t>
-        </is>
-      </c>
+      <c r="M479" s="42" t="inlineStr"/>
       <c r="N479" s="42" t="n"/>
     </row>
     <row r="480">
@@ -33593,13 +33585,13 @@
       <c r="F486" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Tổng cuốc_x000D_
-(1), 33/37
+(1), 0/0
 , Nguồn mobile_x000D_
-(3), 7/7
+(3), 0/0
 , Nguồn điều hành_x000D_
 (5), 0/0
 , Nguồn vãng lai_x000D_
-(6), 26/26
+(6), 0/0
 , Nguồn khách vẫy_x000D_
 (7), 0/0
 , Nguồn Đồng hồ metter_x000D_
@@ -33607,45 +33599,17 @@
 , Nguồn đối tác_x000D_
 (9), 0/0
 , Tổng không đề cử_x000D_
-(11), 2/2
+(11), 0/0
 , Tổng khách hủy_x000D_
 (12), 0/0
 , Tổng lái xe hủy_x000D_
 (13), 0/0
-, Tổng thành công_x000D_
-(14), 30/34
-, Không có lái xe nhận_x000D_
-(15), 1/1
-, Tổng cuốc_x000D_
-(1), 33/37
-, Nguồn mobile_x000D_
-(3), 7/7
-, Nguồn điều hành_x000D_
-(5), 0/0
-, Nguồn vãng lai_x000D_
-(6), 26/26
-, Nguồn khách vẫy_x000D_
-(7), 0/0
-, Nguồn Đồng hồ metter_x000D_
-(8), 0/0
-, Nguồn đối tác_x000D_
-(9), 0/0
-, Tổng không đề cử_x000D_
-(11), 2/2
-, Tổng khách hủy_x000D_
-(12), 0/0
-, Tổng lái xe hủy_x000D_
-(13), 0/0
-, Tổng thành công_x000D_
-(14), 30/34
-, Không có lái xe nhận_x000D_
-(15), 1/1
 </t>
         </is>
       </c>
       <c r="G486" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H486" s="6" t="inlineStr">
@@ -33657,11 +33621,7 @@
       <c r="J486" s="2" t="n"/>
       <c r="K486" s="2" t="n"/>
       <c r="L486" s="2" t="n"/>
-      <c r="M486" s="42" t="inlineStr">
-        <is>
-          <t>Report07_1_TongCuocKhach.png</t>
-        </is>
-      </c>
+      <c r="M486" s="42" t="inlineStr"/>
       <c r="N486" s="42" t="n"/>
     </row>
     <row r="487" ht="75" customHeight="1">
@@ -33691,59 +33651,31 @@
       <c r="F487" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">Tổng cuốc_x000D_
-(1), 41/46
+(1), 27/27
 , Nguồn mobile_x000D_
-(3), 24/24
+(3), 8/8
 , Nguồn điều hành_x000D_
-(5), 10/10
+(5), 0/0
 , Nguồn vãng lai_x000D_
-(6), 7/7
+(6), 19/19
 , Nguồn khách vẫy_x000D_
 (7), 0/0
 , Nguồn Đồng hồ metter_x000D_
-(8), 0/0
+(8), 2/2
 , Nguồn đối tác_x000D_
 (9), 0/0
 , Tổng không đề cử_x000D_
-(11), 23/24
+(11), 0/0
 , Tổng khách hủy_x000D_
-(12), 0/0
+(12), 25/25
 , Tổng lái xe hủy_x000D_
 (13), 0/0
-, Tổng thành công_x000D_
-(14), 17/22
-, Không có lái xe nhận_x000D_
-(15), 1/1
-, Tổng cuốc_x000D_
-(1), 41/46
-, Nguồn mobile_x000D_
-(3), 24/24
-, Nguồn điều hành_x000D_
-(5), 10/10
-, Nguồn vãng lai_x000D_
-(6), 7/7
-, Nguồn khách vẫy_x000D_
-(7), 0/0
-, Nguồn Đồng hồ metter_x000D_
-(8), 0/0
-, Nguồn đối tác_x000D_
-(9), 0/0
-, Tổng không đề cử_x000D_
-(11), 23/24
-, Tổng khách hủy_x000D_
-(12), 0/0
-, Tổng lái xe hủy_x000D_
-(13), 0/0
-, Tổng thành công_x000D_
-(14), 17/22
-, Không có lái xe nhận_x000D_
-(15), 1/1
 </t>
         </is>
       </c>
       <c r="G487" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H487" s="6" t="inlineStr">
@@ -33755,11 +33687,7 @@
       <c r="J487" s="2" t="n"/>
       <c r="K487" s="2" t="n"/>
       <c r="L487" s="2" t="n"/>
-      <c r="M487" s="42" t="inlineStr">
-        <is>
-          <t>Report07_2_TongCuocKhach.png</t>
-        </is>
-      </c>
+      <c r="M487" s="42" t="inlineStr"/>
       <c r="N487" s="42" t="n"/>
     </row>
     <row r="488">
@@ -34690,7 +34618,7 @@
       </c>
       <c r="F516" s="29" t="inlineStr">
         <is>
-          <t>batrinh209a</t>
+          <t>bahlt</t>
         </is>
       </c>
       <c r="G516" s="4" t="inlineStr">
@@ -36038,7 +35966,7 @@
       </c>
       <c r="F558" s="29" t="inlineStr">
         <is>
-          <t>Bui Văn Du</t>
+          <t>Đinh Mạnh Cường 92</t>
         </is>
       </c>
       <c r="G558" s="4" t="inlineStr">
@@ -36082,10 +36010,14 @@
 (Chỉ check tải, không check dữ liệu)</t>
         </is>
       </c>
-      <c r="F559" s="29" t="inlineStr"/>
+      <c r="F559" s="29" t="inlineStr">
+        <is>
+          <t>_BaoCaoDoanhThuTheoLaiXe.xlsx</t>
+        </is>
+      </c>
       <c r="G559" s="4" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H559" s="6" t="inlineStr">
@@ -36097,11 +36029,7 @@
       <c r="J559" s="2" t="n"/>
       <c r="K559" s="2" t="n"/>
       <c r="L559" s="2" t="n"/>
-      <c r="M559" s="42" t="inlineStr">
-        <is>
-          <t>Report49_BaoCaoDoanhThuTheoLaiXe_XuatExcel.png</t>
-        </is>
-      </c>
+      <c r="M559" s="42" t="inlineStr"/>
       <c r="N559" s="42" t="n"/>
     </row>
     <row r="560">
@@ -36167,16 +36095,8 @@
           <t>Chuyển đến trang: "8.4.2 Chi tiết doanh thu từ app lái xe &amp; định vị"</t>
         </is>
       </c>
-      <c r="F562" s="4" t="inlineStr">
-        <is>
-          <t>8.4.2 Chi tiết doanh thu từ app lái xe &amp; định vị</t>
-        </is>
-      </c>
-      <c r="G562" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F562" s="4" t="inlineStr"/>
+      <c r="G562" s="4" t="inlineStr"/>
       <c r="H562" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -36223,7 +36143,7 @@
       </c>
       <c r="F563" s="29" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Taxi thông thường</t>
         </is>
       </c>
       <c r="G563" s="4" t="inlineStr">
@@ -36268,7 +36188,11 @@
         </is>
       </c>
       <c r="F564" s="26" t="inlineStr"/>
-      <c r="G564" s="4" t="inlineStr"/>
+      <c r="G564" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H564" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -36306,7 +36230,11 @@
         </is>
       </c>
       <c r="F565" s="29" t="inlineStr"/>
-      <c r="G565" s="4" t="inlineStr"/>
+      <c r="G565" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="H565" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -36382,16 +36310,8 @@
           <t>Chuyển đến trang: "8.4.3 Thanh toán cuốc khách cho lái xe"</t>
         </is>
       </c>
-      <c r="F568" s="29" t="inlineStr">
-        <is>
-          <t>8.4.3 Thanh toán cuốc khách cho lái xe</t>
-        </is>
-      </c>
-      <c r="G568" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F568" s="29" t="inlineStr"/>
+      <c r="G568" s="4" t="inlineStr"/>
       <c r="H568" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -36432,16 +36352,8 @@
 (Hiển thị Tên lái xe)</t>
         </is>
       </c>
-      <c r="F569" s="29" t="inlineStr">
-        <is>
-          <t>nhatnl</t>
-        </is>
-      </c>
-      <c r="G569" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F569" s="29" t="inlineStr"/>
+      <c r="G569" s="4" t="inlineStr"/>
       <c r="H569" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -36480,11 +36392,7 @@
         </is>
       </c>
       <c r="F570" s="29" t="inlineStr"/>
-      <c r="G570" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="G570" s="4" t="inlineStr"/>
       <c r="H570" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -37041,16 +36949,8 @@
           <t>Chuyển đến trang: "8.4.7 Chi tiết doanh thu từ app lái xe"</t>
         </is>
       </c>
-      <c r="F588" s="29" t="inlineStr">
-        <is>
-          <t>8.4.7 Chi tiết doanh thu từ app lái xe</t>
-        </is>
-      </c>
-      <c r="G588" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F588" s="29" t="inlineStr"/>
+      <c r="G588" s="4" t="inlineStr"/>
       <c r="H588" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -37094,16 +36994,8 @@
 (Hiển thị Biển số)</t>
         </is>
       </c>
-      <c r="F589" s="29" t="inlineStr">
-        <is>
-          <t>hoalt209</t>
-        </is>
-      </c>
-      <c r="G589" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F589" s="29" t="inlineStr"/>
+      <c r="G589" s="4" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -37142,11 +37034,7 @@
         </is>
       </c>
       <c r="F590" s="29" t="inlineStr"/>
-      <c r="G590" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="G590" s="4" t="inlineStr"/>
       <c r="H590" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -38371,16 +38259,8 @@
           <t>Chuyển đến trang: "10.3.1 Thông tin công ty "</t>
         </is>
       </c>
-      <c r="F633" s="29" t="inlineStr">
-        <is>
-          <t>10.3.1 Thông tin công ty</t>
-        </is>
-      </c>
-      <c r="G633" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F633" s="29" t="inlineStr"/>
+      <c r="G633" s="4" t="inlineStr"/>
       <c r="H633" s="2" t="inlineStr">
         <is>
           <t>x</t>
@@ -38720,7 +38600,7 @@
       </c>
       <c r="F641" s="29" t="inlineStr">
         <is>
-          <t>nhóm 1</t>
+          <t>Test gán xe</t>
         </is>
       </c>
       <c r="G641" s="4" t="inlineStr">
@@ -38767,7 +38647,7 @@
       </c>
       <c r="F642" s="29" t="inlineStr">
         <is>
-          <t>nhóm 1</t>
+          <t>Test gán xe</t>
         </is>
       </c>
       <c r="G642" s="4" t="inlineStr">
@@ -40353,7 +40233,7 @@
       </c>
       <c r="F688" s="29" t="inlineStr">
         <is>
-          <t>auto2363</t>
+          <t>auto2093</t>
         </is>
       </c>
       <c r="G688" s="4" t="inlineStr">
@@ -40469,7 +40349,7 @@
       <c r="M690" s="42" t="inlineStr"/>
       <c r="N690" s="42" t="inlineStr">
         <is>
-          <t>auto4346</t>
+          <t>auto4427</t>
         </is>
       </c>
     </row>
@@ -41311,18 +41191,10 @@
 (Chỉ check view)</t>
         </is>
       </c>
-      <c r="F712" s="29" t="inlineStr">
-        <is>
-          <t>STT: 1
-Tên cấu hình: WALLET
-Giá trị: { "isWallet": true, "min": 20000, "isRecharge": true, "isDriverWallet": true, "isDriverRecharge": true, "isCreateCardTrip": true, "requiredPrice": 1, "RechargeType": 3 }
-Kiểu dữ liệu: Kiểu chuỗi
-Ghi chú: {"isWallet":true =&gt; Hiện menu ví trên (Ví tài khoản) ,"min":50000, =&gt; Số tiền tối thiểu cho phép nạp "isRecharge":false, =&gt; Hiện nút nạp tiền ở màn hình ví trên hay không "isDriverWallet":true=&gt; Hiện menu ví dưới (Ví tiền mặt)</t>
-        </is>
-      </c>
+      <c r="F712" s="29" t="inlineStr"/>
       <c r="G712" s="4" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="H712" s="2" t="inlineStr">
@@ -41456,7 +41328,7 @@
 Tên cấu hình: ZOOM_MAP
 Giá trị: {"android": 18, "iOS": 18, "minDistanceToMove": 15}
 Kiểu dữ liệu: Kiểu chuỗi
-Công ty: Cấu hình zoom mặc đinh ở màn hình home (Chỉ áp dụng cho app xamarin)
+Công ty: 
 Ghi chú: </t>
         </is>
       </c>
@@ -41589,9 +41461,9 @@
       <c r="F720" s="29" t="inlineStr">
         <is>
           <t>STT: 1
-Tên cấu hình: YEU_CAU_DOI_MAT_KHAU_THEO_CHU_KY
-Giá trị: False
-Ghi chú: Yêu cầu đổi mật khẩu theo chu kỳ</t>
+Tên cấu hình: XEM_HOADON
+Giá trị: true
+Ghi chú: Xem hóa đơn điện tử ở BC chi tiết doanh thu</t>
         </is>
       </c>
       <c r="G720" s="4" t="inlineStr">
@@ -42397,10 +42269,10 @@
       </c>
       <c r="F747" s="29" t="inlineStr">
         <is>
-          <t>STT: 1
+          <t xml:space="preserve">STT: 1
 Loại thẻ: Hạng vàng
-Màu thẻ: #e3a7ff
-Ghi chú: Thẻ vàng (gold) là loại thẻ tín dụng có hạn mức cao từ trên 50.000.000 đồng, được cấp cho những khách hàng có năng lực tài chính tốt và độ uy tín tín dụng cao. Chủ sở hữu thẻ vàng có cơ hội nhận được nhiều tiện ích và ưu đãi hấp dẫn hơn so với các loại</t>
+Màu thẻ: #eaf037
+Ghi chú: </t>
         </is>
       </c>
       <c r="G747" s="4" t="inlineStr">
@@ -42483,16 +42355,8 @@
           <t>Chuyển đến trang: "10.6.11 Kích hoạt dịch vụ"</t>
         </is>
       </c>
-      <c r="F750" s="29" t="inlineStr">
-        <is>
-          <t>10.6.11 Kích hoạt dịch vụ</t>
-        </is>
-      </c>
-      <c r="G750" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F750" s="29" t="inlineStr"/>
+      <c r="G750" s="4" t="inlineStr"/>
       <c r="H750" s="2" t="inlineStr">
         <is>
           <t>x</t>
@@ -42676,7 +42540,7 @@
       </c>
       <c r="F756" s="29" t="inlineStr">
         <is>
-          <t>Cộng ví tiền mặt khi hoàn thành chuyến thanh toán thẻ. Số dư tài khoản: 20968000đ</t>
+          <t>Cộng ví tiền mặt khi hoàn thành chuyến thanh toán thẻ. Số dư tài khoản: 5341000đ</t>
         </is>
       </c>
       <c r="G756" s="4" t="inlineStr">
@@ -43295,7 +43159,7 @@
       <c r="M771" s="42" t="inlineStr"/>
       <c r="N771" s="67" t="inlineStr">
         <is>
-          <t>Auto_ThongBao_4347</t>
+          <t>Auto_ThongBao_4428</t>
         </is>
       </c>
     </row>
@@ -43370,7 +43234,7 @@
       </c>
       <c r="F773" s="29" t="inlineStr">
         <is>
-          <t>Thông báo test</t>
+          <t>Cập nhật số dư</t>
         </is>
       </c>
       <c r="G773" s="4" t="inlineStr">
@@ -43632,7 +43496,7 @@
       </c>
       <c r="F780" s="29" t="inlineStr">
         <is>
-          <t>Ví tài khoản: -6.000đ, hoàn thành cuốc</t>
+          <t>Ví tài khoản: -2.200đ, hoàn thành cuốc</t>
         </is>
       </c>
       <c r="G780" s="4" t="inlineStr">
@@ -45564,16 +45428,8 @@
           <t>Chuyển đến trang: "10.10.5 Phụ phí theo thời tiết"</t>
         </is>
       </c>
-      <c r="F831" s="29" t="inlineStr">
-        <is>
-          <t>10.10.5 Tăng giá theo thời tiết</t>
-        </is>
-      </c>
-      <c r="G831" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F831" s="29" t="inlineStr"/>
+      <c r="G831" s="4" t="inlineStr"/>
       <c r="H831" s="2" t="inlineStr">
         <is>
           <t>x</t>
@@ -45661,16 +45517,8 @@
           <t>Hiển thị message: "Lưu phụ phí theo thời tiết"</t>
         </is>
       </c>
-      <c r="F833" s="29" t="inlineStr">
-        <is>
-          <t>Lưu phụ phí theo thời tiết</t>
-        </is>
-      </c>
-      <c r="G833" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F833" s="29" t="inlineStr"/>
+      <c r="G833" s="4" t="inlineStr"/>
       <c r="H833" s="2" t="inlineStr">
         <is>
           <t>x</t>
@@ -45748,16 +45596,8 @@
           <t>Hiển thị message: "Xóa phụ phí theo thời tiết thành công"</t>
         </is>
       </c>
-      <c r="F835" s="29" t="inlineStr">
-        <is>
-          <t>Xóa phụ phí theo thời tiết thành công</t>
-        </is>
-      </c>
-      <c r="G835" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F835" s="29" t="inlineStr"/>
+      <c r="G835" s="4" t="inlineStr"/>
       <c r="H835" s="2" t="inlineStr">
         <is>
           <t>x</t>
@@ -46335,11 +46175,7 @@
           <t>Trường "Mã cuốc khách" hiện thị đúng Mã cuốc khách đã nhập</t>
         </is>
       </c>
-      <c r="F853" s="29" t="inlineStr">
-        <is>
-          <t>00072F03</t>
-        </is>
-      </c>
+      <c r="F853" s="29" t="inlineStr"/>
       <c r="G853" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
@@ -47077,16 +46913,8 @@
 2."Cuốc khách không đủ điều kiện xuất hóa đơn"</t>
         </is>
       </c>
-      <c r="F871" s="29" t="inlineStr">
-        <is>
-          <t>Xác nhận xuất hoá đơn khách lẻ</t>
-        </is>
-      </c>
-      <c r="G871" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F871" s="29" t="inlineStr"/>
+      <c r="G871" s="4" t="inlineStr"/>
       <c r="H871" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -47128,16 +46956,8 @@
           <t>Hiển thị thông báo: "Xác nhận không xuất hóa đơn"</t>
         </is>
       </c>
-      <c r="F872" s="29" t="inlineStr">
-        <is>
-          <t>Xác nhận không xuất hóa đơn</t>
-        </is>
-      </c>
-      <c r="G872" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F872" s="29" t="inlineStr"/>
+      <c r="G872" s="4" t="inlineStr"/>
       <c r="H872" s="6" t="inlineStr">
         <is>
           <t>x</t>
@@ -47176,16 +46996,8 @@
 2."Cuốc khách không đủ điều kiện xuất hóa đơn"</t>
         </is>
       </c>
-      <c r="F873" s="29" t="inlineStr">
-        <is>
-          <t>Thông tin xuất hóa đơn</t>
-        </is>
-      </c>
-      <c r="G873" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="F873" s="29" t="inlineStr"/>
+      <c r="G873" s="4" t="inlineStr"/>
       <c r="H873" s="6" t="inlineStr">
         <is>
           <t>x</t>

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4206" uniqueCount="2717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4206" uniqueCount="2718">
   <si>
     <t>WEB STAXI - CHECKLIST AUTOMATION TEST</t>
   </si>
@@ -10430,6 +10430,9 @@
   </si>
   <si>
     <t>Chuyển tới tab "Lịch sử", hiển thị trường: "Tác nhân"</t>
+  </si>
+  <si>
+    <t>đã gộp vào báo cáo 6.4.3</t>
   </si>
 </sst>
 </file>
@@ -10866,14 +10869,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10883,15 +10889,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="284">
+  <dxfs count="285">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -25437,13 +25450,13 @@
       <c r="L1" s="4"/>
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32"/>
@@ -25462,14 +25475,14 @@
       <c r="L2" s="4"/>
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
     </row>
     <row r="3" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
@@ -25491,19 +25504,19 @@
       <c r="I3" s="80"/>
       <c r="J3" s="80"/>
       <c r="K3" s="80"/>
-      <c r="L3" s="87" t="s">
+      <c r="L3" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="88"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
     </row>
     <row r="4" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32"/>
@@ -25531,18 +25544,18 @@
       <c r="L4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="86" t="s">
+      <c r="M4" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="83"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
     </row>
     <row r="5" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="32"/>
@@ -25570,18 +25583,18 @@
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="82" t="s">
+      <c r="M5" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="83"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+      <c r="T5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
     </row>
     <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32"/>
@@ -25609,10 +25622,10 @@
       <c r="L6" s="6">
         <v>2</v>
       </c>
-      <c r="M6" s="82" t="s">
+      <c r="M6" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="83"/>
+      <c r="N6" s="85"/>
       <c r="O6" s="81"/>
     </row>
     <row r="7" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -25622,7 +25635,7 @@
       </c>
       <c r="C7" s="15">
         <f>COUNTIF(K:K,"x")</f>
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D7" s="15">
         <f>COUNTIFS(G:G,"Pass",K:K,"x")</f>
@@ -25641,10 +25654,10 @@
       <c r="L7" s="6">
         <v>3</v>
       </c>
-      <c r="M7" s="82" t="s">
+      <c r="M7" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="83"/>
+      <c r="N7" s="85"/>
       <c r="O7" s="81"/>
     </row>
     <row r="8" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -33320,12 +33333,12 @@
       </c>
       <c r="F301" s="29"/>
       <c r="G301" s="4"/>
-      <c r="H301" s="2"/>
+      <c r="H301" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
-      <c r="K301" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="K301" s="2"/>
       <c r="L301" s="2"/>
       <c r="M301" s="42"/>
       <c r="N301" s="42"/>
@@ -33346,12 +33359,12 @@
       </c>
       <c r="F302" s="29"/>
       <c r="G302" s="4"/>
-      <c r="H302" s="2"/>
+      <c r="H302" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
-      <c r="K302" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="K302" s="2"/>
       <c r="L302" s="2"/>
       <c r="M302" s="42"/>
       <c r="N302" s="42"/>
@@ -33372,12 +33385,12 @@
       </c>
       <c r="F303" s="29"/>
       <c r="G303" s="4"/>
-      <c r="H303" s="2"/>
+      <c r="H303" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
-      <c r="K303" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="K303" s="2"/>
       <c r="L303" s="2"/>
       <c r="M303" s="42"/>
       <c r="N303" s="42"/>
@@ -33433,15 +33446,15 @@
       </c>
       <c r="F306" s="29"/>
       <c r="G306" s="4"/>
-      <c r="H306" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="H306" s="6"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
       <c r="K306" s="2"/>
       <c r="L306" s="2"/>
       <c r="M306" s="42"/>
-      <c r="N306" s="42"/>
+      <c r="N306" s="45" t="s">
+        <v>2717</v>
+      </c>
     </row>
     <row r="307" spans="1:14" ht="78.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="37" t="s">
@@ -33459,15 +33472,15 @@
       </c>
       <c r="F307" s="29"/>
       <c r="G307" s="4"/>
-      <c r="H307" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="H307" s="6"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
       <c r="K307" s="2"/>
       <c r="L307" s="2"/>
       <c r="M307" s="42"/>
-      <c r="N307" s="42"/>
+      <c r="N307" s="45" t="s">
+        <v>2717</v>
+      </c>
     </row>
     <row r="308" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="37" t="s">
@@ -33485,15 +33498,15 @@
       </c>
       <c r="F308" s="29"/>
       <c r="G308" s="4"/>
-      <c r="H308" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="H308" s="6"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
       <c r="M308" s="42"/>
-      <c r="N308" s="42"/>
+      <c r="N308" s="45" t="s">
+        <v>2717</v>
+      </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B309" s="37"/>
@@ -48845,1421 +48858,1426 @@
     <mergeCell ref="O4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="G19:G26 G30:G51 G53:G67 G70:G86 G91:G101 G104:G109 G111:G124 G127:G157 G159:G190 G197 G200:G209 G211:G213 G215:G217 G219 G222:G229 G231:G248 G251 G253:G257 G259:G266 G268:G279 G281:G288 G291:G294 G299 G304 G306:G309 G314 G319 G324 G329 G334 G336 G338:G340 G342 G346 G349:G367 G370:G377 G379:G380 G384:G388 G390 G392:G421 G427:G433 G436:G439 G444 G446:G450 G455 G457 G462:G472 G476:G479 G483:G488 G510:G512 G515:G517 G557:G559 G562:G565 G568:G570 G588:G591 G601 G620 G624 G630 G633:G638 G640:G649 G651 G653:G656 G658 G660:G665 G667:G674 G676:G684 G687:G699 G701:G702 G704:G708 G711:G713 G715:G717 G719:G721 G723:G725 G729 G733 G737 G740 G744 G746:G748 G750 G752 G755:G776 G778 G780:G781 G806 G809 G811 G814 G816 G818 G821 G826 G828 G831:G836 G842 G847 L1:L2 L8:L28 L30:L51 L70:L86 L92:L101 L104:L109 L111:L124 L127:L145 L147:L157 L160 L162:L190 L197 L201:L209 L213 L217 L222:L229 L232:L248 L253:L266 L269:L279 L281:L288 L291:L294 L299 L304 L309 L314 L319 L324 L329 L334 L338:L340 L346 L350:L367 L370:L377 L384:L388 L392:L421 L425:L433 L436:L439 L444 L450 L455 L462:L472 L484:L488 L555 L591 L601 L620 L630 L633:L638 L640:L649 L653:L656 L660:L665 L667:L674 L676:L684 L688:L699 L704:L708 L712:L713 L717 L721 L725 L729 L733 L737 L740 L744 L748 L752 L756:L776 L808:L812 L816:L819 L823:L829 L852:L881 L883:L887 L890:L931 L935:L1048576">
-    <cfRule type="cellIs" dxfId="283" priority="478" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="479" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12:G16">
-    <cfRule type="cellIs" dxfId="282" priority="411" operator="equal">
+    <cfRule type="cellIs" dxfId="283" priority="412" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L29">
+    <cfRule type="cellIs" dxfId="282" priority="306" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L91">
     <cfRule type="cellIs" dxfId="281" priority="305" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L91">
+  <conditionalFormatting sqref="L90">
     <cfRule type="cellIs" dxfId="280" priority="304" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L90">
+  <conditionalFormatting sqref="L52">
     <cfRule type="cellIs" dxfId="279" priority="303" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L52">
+  <conditionalFormatting sqref="L87">
     <cfRule type="cellIs" dxfId="278" priority="302" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L87">
+  <conditionalFormatting sqref="L88">
     <cfRule type="cellIs" dxfId="277" priority="301" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L88">
+  <conditionalFormatting sqref="L89">
     <cfRule type="cellIs" dxfId="276" priority="300" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L89">
+  <conditionalFormatting sqref="L102">
     <cfRule type="cellIs" dxfId="275" priority="299" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L102">
+  <conditionalFormatting sqref="L103">
     <cfRule type="cellIs" dxfId="274" priority="298" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L103">
+  <conditionalFormatting sqref="G68 L53:L68">
     <cfRule type="cellIs" dxfId="273" priority="297" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G68 L53:L68">
+  <conditionalFormatting sqref="L69">
     <cfRule type="cellIs" dxfId="272" priority="296" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L69">
+  <conditionalFormatting sqref="L110">
     <cfRule type="cellIs" dxfId="271" priority="295" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L110">
+  <conditionalFormatting sqref="L125:L126">
     <cfRule type="cellIs" dxfId="270" priority="294" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L125:L126">
+  <conditionalFormatting sqref="L159">
     <cfRule type="cellIs" dxfId="269" priority="293" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L159">
+  <conditionalFormatting sqref="L158">
     <cfRule type="cellIs" dxfId="268" priority="292" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L158">
-    <cfRule type="cellIs" dxfId="267" priority="291" operator="equal">
+  <conditionalFormatting sqref="L200">
+    <cfRule type="cellIs" dxfId="267" priority="289" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L200">
+  <conditionalFormatting sqref="L198:L199">
     <cfRule type="cellIs" dxfId="266" priority="288" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L198:L199">
+  <conditionalFormatting sqref="L212">
     <cfRule type="cellIs" dxfId="265" priority="287" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L212">
+  <conditionalFormatting sqref="L211">
     <cfRule type="cellIs" dxfId="264" priority="286" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L211">
+  <conditionalFormatting sqref="L210">
     <cfRule type="cellIs" dxfId="263" priority="285" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L210">
+  <conditionalFormatting sqref="L216">
     <cfRule type="cellIs" dxfId="262" priority="284" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L216">
+  <conditionalFormatting sqref="L215">
     <cfRule type="cellIs" dxfId="261" priority="283" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L215">
+  <conditionalFormatting sqref="L214">
     <cfRule type="cellIs" dxfId="260" priority="282" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L214">
+  <conditionalFormatting sqref="G221 L220:L221">
     <cfRule type="cellIs" dxfId="259" priority="281" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G221 L220:L221">
+  <conditionalFormatting sqref="L219">
     <cfRule type="cellIs" dxfId="258" priority="280" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L219">
+  <conditionalFormatting sqref="L218">
     <cfRule type="cellIs" dxfId="257" priority="279" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L218">
+  <conditionalFormatting sqref="L231">
     <cfRule type="cellIs" dxfId="256" priority="278" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L231">
+  <conditionalFormatting sqref="L230">
     <cfRule type="cellIs" dxfId="255" priority="277" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L230">
+  <conditionalFormatting sqref="G252 L252">
     <cfRule type="cellIs" dxfId="254" priority="276" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G252 L252">
+  <conditionalFormatting sqref="L251">
     <cfRule type="cellIs" dxfId="253" priority="275" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L251">
+  <conditionalFormatting sqref="L250">
     <cfRule type="cellIs" dxfId="252" priority="274" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L250">
+  <conditionalFormatting sqref="L249">
     <cfRule type="cellIs" dxfId="251" priority="273" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L249">
+  <conditionalFormatting sqref="L268">
     <cfRule type="cellIs" dxfId="250" priority="272" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L268">
+  <conditionalFormatting sqref="L267">
     <cfRule type="cellIs" dxfId="249" priority="271" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L267">
+  <conditionalFormatting sqref="L280">
     <cfRule type="cellIs" dxfId="248" priority="270" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L280">
+  <conditionalFormatting sqref="G290 L290">
     <cfRule type="cellIs" dxfId="247" priority="269" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G290 L290">
+  <conditionalFormatting sqref="L289">
     <cfRule type="cellIs" dxfId="246" priority="268" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L289">
+  <conditionalFormatting sqref="G296:G298 L296:L298">
     <cfRule type="cellIs" dxfId="245" priority="267" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G296:G298 L296:L298">
+  <conditionalFormatting sqref="G295 L295">
     <cfRule type="cellIs" dxfId="244" priority="266" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G295 L295">
+  <conditionalFormatting sqref="G301:G302 L301:L303">
     <cfRule type="cellIs" dxfId="243" priority="265" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G301:G302 L301:L303">
+  <conditionalFormatting sqref="G300 L300">
     <cfRule type="cellIs" dxfId="242" priority="264" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G300 L300">
+  <conditionalFormatting sqref="L306:L308">
     <cfRule type="cellIs" dxfId="241" priority="263" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L306:L308">
+  <conditionalFormatting sqref="G305 L305">
     <cfRule type="cellIs" dxfId="240" priority="262" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G305 L305">
+  <conditionalFormatting sqref="G311:G313 L311:L313">
     <cfRule type="cellIs" dxfId="239" priority="261" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G311:G313 L311:L313">
+  <conditionalFormatting sqref="G310 L310">
     <cfRule type="cellIs" dxfId="238" priority="260" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G310 L310">
+  <conditionalFormatting sqref="G316:G318 L316:L318">
     <cfRule type="cellIs" dxfId="237" priority="259" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G316:G318 L316:L318">
+  <conditionalFormatting sqref="G315 L315">
     <cfRule type="cellIs" dxfId="236" priority="258" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G315 L315">
+  <conditionalFormatting sqref="G321:G323 L321:L323">
     <cfRule type="cellIs" dxfId="235" priority="257" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G321:G323 L321:L323">
+  <conditionalFormatting sqref="G320 L320">
     <cfRule type="cellIs" dxfId="234" priority="256" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G320 L320">
+  <conditionalFormatting sqref="G326:G328 L326:L328">
     <cfRule type="cellIs" dxfId="233" priority="255" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G326:G328 L326:L328">
+  <conditionalFormatting sqref="G325 L325">
     <cfRule type="cellIs" dxfId="232" priority="254" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G325 L325">
+  <conditionalFormatting sqref="G331:G333 L331:L333">
     <cfRule type="cellIs" dxfId="231" priority="253" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G331:G333 L331:L333">
+  <conditionalFormatting sqref="G330 L330">
     <cfRule type="cellIs" dxfId="230" priority="252" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G330 L330">
+  <conditionalFormatting sqref="G337 L337">
     <cfRule type="cellIs" dxfId="229" priority="251" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G337 L337">
+  <conditionalFormatting sqref="L336">
     <cfRule type="cellIs" dxfId="228" priority="250" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L336">
+  <conditionalFormatting sqref="L335">
     <cfRule type="cellIs" dxfId="227" priority="249" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L335">
+  <conditionalFormatting sqref="G344:G345 L344:L345">
     <cfRule type="cellIs" dxfId="226" priority="248" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G344:G345 L344:L345">
+  <conditionalFormatting sqref="G343 L343">
     <cfRule type="cellIs" dxfId="225" priority="247" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G343 L343">
+  <conditionalFormatting sqref="L342">
     <cfRule type="cellIs" dxfId="224" priority="246" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L342">
+  <conditionalFormatting sqref="L341">
     <cfRule type="cellIs" dxfId="223" priority="245" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L341">
+  <conditionalFormatting sqref="L349">
     <cfRule type="cellIs" dxfId="222" priority="244" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L349">
+  <conditionalFormatting sqref="L348">
     <cfRule type="cellIs" dxfId="221" priority="243" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L348">
+  <conditionalFormatting sqref="L347">
     <cfRule type="cellIs" dxfId="220" priority="242" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L347">
+  <conditionalFormatting sqref="G369 L369">
     <cfRule type="cellIs" dxfId="219" priority="241" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G369 L369">
+  <conditionalFormatting sqref="L368">
     <cfRule type="cellIs" dxfId="218" priority="240" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L368">
+  <conditionalFormatting sqref="G381:G383 L379:L383">
     <cfRule type="cellIs" dxfId="217" priority="239" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G381:G383 L379:L383">
+  <conditionalFormatting sqref="G378 L378">
     <cfRule type="cellIs" dxfId="216" priority="238" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G378 L378">
+  <conditionalFormatting sqref="G391 L390:L391">
     <cfRule type="cellIs" dxfId="215" priority="237" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G391 L390:L391">
+  <conditionalFormatting sqref="G389 L389">
     <cfRule type="cellIs" dxfId="214" priority="236" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G389 L389">
+  <conditionalFormatting sqref="G423:G424 L423:L424">
     <cfRule type="cellIs" dxfId="213" priority="235" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G423:G424 L423:L424">
+  <conditionalFormatting sqref="G422 L422">
     <cfRule type="cellIs" dxfId="212" priority="234" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G422 L422">
+  <conditionalFormatting sqref="G435 L435">
     <cfRule type="cellIs" dxfId="211" priority="233" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G435 L435">
+  <conditionalFormatting sqref="G434 L434">
     <cfRule type="cellIs" dxfId="210" priority="232" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G434 L434">
+  <conditionalFormatting sqref="G442:G443 L442:L443">
     <cfRule type="cellIs" dxfId="209" priority="231" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G442:G443 L442:L443">
+  <conditionalFormatting sqref="G441 L441">
     <cfRule type="cellIs" dxfId="208" priority="230" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G441 L441">
+  <conditionalFormatting sqref="G440 L440">
     <cfRule type="cellIs" dxfId="207" priority="229" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G440 L440">
+  <conditionalFormatting sqref="L447:L449">
     <cfRule type="cellIs" dxfId="206" priority="228" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L447:L449">
+  <conditionalFormatting sqref="L446">
     <cfRule type="cellIs" dxfId="205" priority="227" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L446">
+  <conditionalFormatting sqref="G445 L445">
     <cfRule type="cellIs" dxfId="204" priority="226" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G445 L445">
+  <conditionalFormatting sqref="G453:G454 L453:L454">
     <cfRule type="cellIs" dxfId="203" priority="225" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G453:G454 L453:L454">
+  <conditionalFormatting sqref="G452 L452">
     <cfRule type="cellIs" dxfId="202" priority="224" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G452 L452">
+  <conditionalFormatting sqref="G451 L451">
     <cfRule type="cellIs" dxfId="201" priority="223" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G451 L451">
+  <conditionalFormatting sqref="G458:G460 L458:L460">
     <cfRule type="cellIs" dxfId="200" priority="222" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G458:G460 L458:L460">
+  <conditionalFormatting sqref="L457">
     <cfRule type="cellIs" dxfId="199" priority="221" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L457">
+  <conditionalFormatting sqref="G456 L456">
     <cfRule type="cellIs" dxfId="198" priority="220" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G456 L456">
-    <cfRule type="cellIs" dxfId="197" priority="219" operator="equal">
+  <conditionalFormatting sqref="L474">
+    <cfRule type="cellIs" dxfId="197" priority="218" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L474">
+  <conditionalFormatting sqref="L473">
     <cfRule type="cellIs" dxfId="196" priority="217" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L473">
-    <cfRule type="cellIs" dxfId="195" priority="216" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G475 L475">
-    <cfRule type="cellIs" dxfId="194" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="212" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G480:G481 G586 L477:L481 L586">
+    <cfRule type="cellIs" dxfId="194" priority="214" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L476">
     <cfRule type="cellIs" dxfId="193" priority="213" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L476">
-    <cfRule type="cellIs" dxfId="192" priority="212" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G482 L482">
-    <cfRule type="cellIs" dxfId="191" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="208" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G493 G498 G503 G508 G513 G518 G523 G534 G539 G544 G549 G554 G560 G566 G571 G576 G581 L493 L498 L503 L508 L513 L518 L523 L534 L539 L544 L549 L554 L560 L566 L571 L576 L581">
+    <cfRule type="cellIs" dxfId="191" priority="210" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L483">
     <cfRule type="cellIs" dxfId="190" priority="209" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L483">
-    <cfRule type="cellIs" dxfId="189" priority="208" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G489 L489">
-    <cfRule type="cellIs" dxfId="188" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="205" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G491:G492 L491:L492">
+    <cfRule type="cellIs" dxfId="188" priority="207" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G490 L490">
     <cfRule type="cellIs" dxfId="187" priority="206" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G490 L490">
-    <cfRule type="cellIs" dxfId="186" priority="205" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G494 L494">
-    <cfRule type="cellIs" dxfId="185" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="202" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G496:G497 L496:L497">
+    <cfRule type="cellIs" dxfId="185" priority="204" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G495 L495">
     <cfRule type="cellIs" dxfId="184" priority="203" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G495 L495">
-    <cfRule type="cellIs" dxfId="183" priority="202" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G499 L499">
-    <cfRule type="cellIs" dxfId="182" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="199" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G501:G502 L501:L502">
+    <cfRule type="cellIs" dxfId="182" priority="201" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G500 L500">
     <cfRule type="cellIs" dxfId="181" priority="200" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G500 L500">
-    <cfRule type="cellIs" dxfId="180" priority="199" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G504 L504">
-    <cfRule type="cellIs" dxfId="179" priority="195" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="196" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G507 L506:L507">
+    <cfRule type="cellIs" dxfId="179" priority="198" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G505 L505">
     <cfRule type="cellIs" dxfId="178" priority="197" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G505 L505">
-    <cfRule type="cellIs" dxfId="177" priority="196" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G509 L509">
-    <cfRule type="cellIs" dxfId="176" priority="192" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="193" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L511:L512">
+    <cfRule type="cellIs" dxfId="176" priority="195" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L510">
     <cfRule type="cellIs" dxfId="175" priority="194" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L510">
-    <cfRule type="cellIs" dxfId="174" priority="193" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G514 L514">
-    <cfRule type="cellIs" dxfId="173" priority="189" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="190" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L516:L517">
+    <cfRule type="cellIs" dxfId="173" priority="192" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L515">
     <cfRule type="cellIs" dxfId="172" priority="191" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L515">
-    <cfRule type="cellIs" dxfId="171" priority="190" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G519 L519">
-    <cfRule type="cellIs" dxfId="170" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="187" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G521:G522 L521:L522">
+    <cfRule type="cellIs" dxfId="170" priority="189" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G520 L520">
     <cfRule type="cellIs" dxfId="169" priority="188" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G520 L520">
-    <cfRule type="cellIs" dxfId="168" priority="187" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G524 L524">
-    <cfRule type="cellIs" dxfId="167" priority="183" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="184" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G526:G528 L526:L528">
+    <cfRule type="cellIs" dxfId="167" priority="186" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G525 L525">
     <cfRule type="cellIs" dxfId="166" priority="185" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G525 L525">
-    <cfRule type="cellIs" dxfId="165" priority="184" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L529">
-    <cfRule type="cellIs" dxfId="164" priority="182" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="183" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G530 L530">
-    <cfRule type="cellIs" dxfId="163" priority="179" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="180" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G532:G533 L532:L533">
+    <cfRule type="cellIs" dxfId="163" priority="182" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G531 L531">
     <cfRule type="cellIs" dxfId="162" priority="181" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G531 L531">
-    <cfRule type="cellIs" dxfId="161" priority="180" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G535 L535">
-    <cfRule type="cellIs" dxfId="160" priority="176" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="177" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G537:G538 L537:L538">
+    <cfRule type="cellIs" dxfId="160" priority="179" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G536 L536">
     <cfRule type="cellIs" dxfId="159" priority="178" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G536 L536">
-    <cfRule type="cellIs" dxfId="158" priority="177" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G540 L540">
-    <cfRule type="cellIs" dxfId="157" priority="173" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="174" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G542:G543 L542:L543">
+    <cfRule type="cellIs" dxfId="157" priority="176" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G541 L541">
     <cfRule type="cellIs" dxfId="156" priority="175" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G541 L541">
-    <cfRule type="cellIs" dxfId="155" priority="174" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G545 L545">
-    <cfRule type="cellIs" dxfId="154" priority="170" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="171" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G547:G548 L547:L548">
+    <cfRule type="cellIs" dxfId="154" priority="173" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G546 L546">
     <cfRule type="cellIs" dxfId="153" priority="172" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G546 L546">
-    <cfRule type="cellIs" dxfId="152" priority="171" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G550 L550">
-    <cfRule type="cellIs" dxfId="151" priority="167" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="168" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G552:G553 L552:L553">
+    <cfRule type="cellIs" dxfId="151" priority="170" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G551 L551">
     <cfRule type="cellIs" dxfId="150" priority="169" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G551 L551">
-    <cfRule type="cellIs" dxfId="149" priority="168" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G556 L556">
-    <cfRule type="cellIs" dxfId="148" priority="164" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="165" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L558:L559">
+    <cfRule type="cellIs" dxfId="148" priority="167" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L557">
     <cfRule type="cellIs" dxfId="147" priority="166" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L557">
-    <cfRule type="cellIs" dxfId="146" priority="165" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G561 L561">
-    <cfRule type="cellIs" dxfId="145" priority="161" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="162" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L563:L565">
+    <cfRule type="cellIs" dxfId="145" priority="164" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L562">
     <cfRule type="cellIs" dxfId="144" priority="163" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L562">
-    <cfRule type="cellIs" dxfId="143" priority="162" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G567 L567">
-    <cfRule type="cellIs" dxfId="142" priority="158" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="159" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L569:L570">
+    <cfRule type="cellIs" dxfId="142" priority="161" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L568">
     <cfRule type="cellIs" dxfId="141" priority="160" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L568">
-    <cfRule type="cellIs" dxfId="140" priority="159" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G572 L572">
-    <cfRule type="cellIs" dxfId="139" priority="155" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="156" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G574:G575 L574:L575">
+    <cfRule type="cellIs" dxfId="139" priority="158" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G573 L573">
     <cfRule type="cellIs" dxfId="138" priority="157" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G573 L573">
-    <cfRule type="cellIs" dxfId="137" priority="156" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G577 L577">
-    <cfRule type="cellIs" dxfId="136" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="153" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G579:G580 L579:L580">
+    <cfRule type="cellIs" dxfId="136" priority="155" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G578 L578">
     <cfRule type="cellIs" dxfId="135" priority="154" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G578 L578">
-    <cfRule type="cellIs" dxfId="134" priority="153" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G582 L582">
-    <cfRule type="cellIs" dxfId="133" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="150" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G584:G585 L584:L585">
+    <cfRule type="cellIs" dxfId="133" priority="152" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G583 L583">
     <cfRule type="cellIs" dxfId="132" priority="151" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G583 L583">
-    <cfRule type="cellIs" dxfId="131" priority="150" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G587 L587">
-    <cfRule type="cellIs" dxfId="130" priority="146" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="147" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L589:L590">
+    <cfRule type="cellIs" dxfId="130" priority="149" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L588">
     <cfRule type="cellIs" dxfId="129" priority="148" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L588">
-    <cfRule type="cellIs" dxfId="128" priority="147" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G592 L592">
-    <cfRule type="cellIs" dxfId="127" priority="143" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="144" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G594:G596 G608 L594:L596 L608">
+    <cfRule type="cellIs" dxfId="127" priority="146" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G593 L593">
     <cfRule type="cellIs" dxfId="126" priority="145" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G593 L593">
-    <cfRule type="cellIs" dxfId="125" priority="144" operator="equal">
+  <conditionalFormatting sqref="L622">
+    <cfRule type="cellIs" dxfId="125" priority="143" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L622">
+  <conditionalFormatting sqref="L621">
     <cfRule type="cellIs" dxfId="124" priority="142" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L621">
+  <conditionalFormatting sqref="G623 L623">
     <cfRule type="cellIs" dxfId="123" priority="141" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G623 L623">
+  <conditionalFormatting sqref="G625 L625">
     <cfRule type="cellIs" dxfId="122" priority="140" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G625 L625">
+  <conditionalFormatting sqref="L624">
     <cfRule type="cellIs" dxfId="121" priority="139" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L624">
+  <conditionalFormatting sqref="G626:G629 L626:L629">
     <cfRule type="cellIs" dxfId="120" priority="138" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G626:G629 L626:L629">
+  <conditionalFormatting sqref="L631">
     <cfRule type="cellIs" dxfId="119" priority="137" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L631">
+  <conditionalFormatting sqref="G632 L632">
     <cfRule type="cellIs" dxfId="118" priority="136" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G632 L632">
+  <conditionalFormatting sqref="G652 L651:L652">
     <cfRule type="cellIs" dxfId="117" priority="135" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G652 L651:L652">
+  <conditionalFormatting sqref="G650 L650">
     <cfRule type="cellIs" dxfId="116" priority="134" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G650 L650">
+  <conditionalFormatting sqref="G659 L658:L659">
     <cfRule type="cellIs" dxfId="115" priority="133" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G659 L658:L659">
+  <conditionalFormatting sqref="G657 L657">
     <cfRule type="cellIs" dxfId="114" priority="132" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G657 L657">
+  <conditionalFormatting sqref="L687">
     <cfRule type="cellIs" dxfId="113" priority="131" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L687">
+  <conditionalFormatting sqref="L685">
     <cfRule type="cellIs" dxfId="112" priority="130" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L685">
+  <conditionalFormatting sqref="G686 L686">
     <cfRule type="cellIs" dxfId="111" priority="129" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G686 L686">
+  <conditionalFormatting sqref="G703 L703">
     <cfRule type="cellIs" dxfId="110" priority="128" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G703 L703">
+  <conditionalFormatting sqref="L701:L702">
     <cfRule type="cellIs" dxfId="109" priority="127" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L701:L702">
+  <conditionalFormatting sqref="G700 L700">
     <cfRule type="cellIs" dxfId="108" priority="126" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G700 L700">
+  <conditionalFormatting sqref="L711">
     <cfRule type="cellIs" dxfId="107" priority="125" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L711">
+  <conditionalFormatting sqref="L709">
     <cfRule type="cellIs" dxfId="106" priority="124" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L709">
+  <conditionalFormatting sqref="G710 L710">
     <cfRule type="cellIs" dxfId="105" priority="123" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G710 L710">
+  <conditionalFormatting sqref="L716">
     <cfRule type="cellIs" dxfId="104" priority="122" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L716">
+  <conditionalFormatting sqref="L715">
     <cfRule type="cellIs" dxfId="103" priority="121" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L715">
+  <conditionalFormatting sqref="G714 L714">
     <cfRule type="cellIs" dxfId="102" priority="120" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G714 L714">
+  <conditionalFormatting sqref="L720">
     <cfRule type="cellIs" dxfId="101" priority="119" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L720">
+  <conditionalFormatting sqref="L719">
     <cfRule type="cellIs" dxfId="100" priority="118" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L719">
+  <conditionalFormatting sqref="G718 L718">
     <cfRule type="cellIs" dxfId="99" priority="117" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G718 L718">
+  <conditionalFormatting sqref="L724">
     <cfRule type="cellIs" dxfId="98" priority="116" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L724">
+  <conditionalFormatting sqref="L723">
     <cfRule type="cellIs" dxfId="97" priority="115" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L723">
+  <conditionalFormatting sqref="G722 L722">
     <cfRule type="cellIs" dxfId="96" priority="114" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G722 L722">
+  <conditionalFormatting sqref="G728 L728">
     <cfRule type="cellIs" dxfId="95" priority="113" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G728 L728">
+  <conditionalFormatting sqref="G727 L727">
     <cfRule type="cellIs" dxfId="94" priority="112" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G727 L727">
+  <conditionalFormatting sqref="G726 L726">
     <cfRule type="cellIs" dxfId="93" priority="111" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G726 L726">
+  <conditionalFormatting sqref="G732 L732">
     <cfRule type="cellIs" dxfId="92" priority="110" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G732 L732">
+  <conditionalFormatting sqref="G731 L731">
     <cfRule type="cellIs" dxfId="91" priority="109" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G731 L731">
+  <conditionalFormatting sqref="G730 L730">
     <cfRule type="cellIs" dxfId="90" priority="108" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G730 L730">
-    <cfRule type="cellIs" dxfId="89" priority="107" operator="equal">
+  <conditionalFormatting sqref="G736 L736">
+    <cfRule type="cellIs" dxfId="89" priority="104" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G736 L736">
+  <conditionalFormatting sqref="G735 L735">
     <cfRule type="cellIs" dxfId="88" priority="103" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G735 L735">
+  <conditionalFormatting sqref="G734 L734">
     <cfRule type="cellIs" dxfId="87" priority="102" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G734 L734">
+  <conditionalFormatting sqref="G739 L739">
     <cfRule type="cellIs" dxfId="86" priority="101" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G739 L739">
+  <conditionalFormatting sqref="G738 L738">
     <cfRule type="cellIs" dxfId="85" priority="100" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G738 L738">
+  <conditionalFormatting sqref="G743 L743">
     <cfRule type="cellIs" dxfId="84" priority="99" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G743 L743">
+  <conditionalFormatting sqref="G742 L742">
     <cfRule type="cellIs" dxfId="83" priority="98" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G742 L742">
+  <conditionalFormatting sqref="G741 L741">
     <cfRule type="cellIs" dxfId="82" priority="97" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G741 L741">
+  <conditionalFormatting sqref="L747">
     <cfRule type="cellIs" dxfId="81" priority="96" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L747">
+  <conditionalFormatting sqref="L746">
     <cfRule type="cellIs" dxfId="80" priority="95" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L746">
+  <conditionalFormatting sqref="G745 L745">
     <cfRule type="cellIs" dxfId="79" priority="94" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G745 L745">
+  <conditionalFormatting sqref="G751 L751">
     <cfRule type="cellIs" dxfId="78" priority="93" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G751 L751">
+  <conditionalFormatting sqref="L750">
     <cfRule type="cellIs" dxfId="77" priority="92" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L750">
+  <conditionalFormatting sqref="G749 L749">
     <cfRule type="cellIs" dxfId="76" priority="91" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G749 L749">
+  <conditionalFormatting sqref="L755">
     <cfRule type="cellIs" dxfId="75" priority="90" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L755">
+  <conditionalFormatting sqref="L753">
     <cfRule type="cellIs" dxfId="74" priority="89" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L753">
+  <conditionalFormatting sqref="G754 L754">
     <cfRule type="cellIs" dxfId="73" priority="88" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G754 L754">
-    <cfRule type="cellIs" dxfId="72" priority="87" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G777 L777">
-    <cfRule type="cellIs" dxfId="71" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="85" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G808 G810 G812 G819 G823:G825 G827 G829">
-    <cfRule type="cellIs" dxfId="70" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="83" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G807 L807">
+    <cfRule type="cellIs" dxfId="70" priority="81" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L806">
     <cfRule type="cellIs" dxfId="69" priority="80" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L806">
+  <conditionalFormatting sqref="L804">
     <cfRule type="cellIs" dxfId="68" priority="79" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L804">
+  <conditionalFormatting sqref="G805 L805">
     <cfRule type="cellIs" dxfId="67" priority="78" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G805 L805">
+  <conditionalFormatting sqref="G815 L815">
     <cfRule type="cellIs" dxfId="66" priority="77" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G815 L815">
+  <conditionalFormatting sqref="L814">
     <cfRule type="cellIs" dxfId="65" priority="76" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L814">
+  <conditionalFormatting sqref="G813 L813">
     <cfRule type="cellIs" dxfId="64" priority="75" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G813 L813">
+  <conditionalFormatting sqref="G822 L822">
     <cfRule type="cellIs" dxfId="63" priority="74" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G822 L822">
+  <conditionalFormatting sqref="L821">
     <cfRule type="cellIs" dxfId="62" priority="73" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L821">
+  <conditionalFormatting sqref="G820 L820">
     <cfRule type="cellIs" dxfId="61" priority="72" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G820 L820">
+  <conditionalFormatting sqref="L833:L836 L842 L847">
     <cfRule type="cellIs" dxfId="60" priority="71" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L833:L836 L842 L847">
-    <cfRule type="cellIs" dxfId="59" priority="70" operator="equal">
+  <conditionalFormatting sqref="L832">
+    <cfRule type="cellIs" dxfId="59" priority="69" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L832">
+  <conditionalFormatting sqref="L831">
     <cfRule type="cellIs" dxfId="58" priority="68" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L831">
+  <conditionalFormatting sqref="G830 L830">
     <cfRule type="cellIs" dxfId="57" priority="67" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G830 L830">
-    <cfRule type="cellIs" dxfId="56" priority="66" operator="equal">
+  <conditionalFormatting sqref="H652">
+    <cfRule type="cellIs" dxfId="56" priority="64" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H652">
+  <conditionalFormatting sqref="H653">
     <cfRule type="cellIs" dxfId="55" priority="63" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H653">
+  <conditionalFormatting sqref="H654">
     <cfRule type="cellIs" dxfId="54" priority="62" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H654">
+  <conditionalFormatting sqref="H655">
     <cfRule type="cellIs" dxfId="53" priority="61" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H655">
-    <cfRule type="cellIs" dxfId="52" priority="60" operator="equal">
+  <conditionalFormatting sqref="K262:K264">
+    <cfRule type="cellIs" dxfId="52" priority="57" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K262:K264">
+  <conditionalFormatting sqref="G461 L461">
     <cfRule type="cellIs" dxfId="51" priority="56" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G461 L461">
+  <conditionalFormatting sqref="L780:L803">
     <cfRule type="cellIs" dxfId="50" priority="55" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L780:L803">
+  <conditionalFormatting sqref="L779">
     <cfRule type="cellIs" dxfId="49" priority="54" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L779">
+  <conditionalFormatting sqref="L778">
     <cfRule type="cellIs" dxfId="48" priority="53" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L778">
+  <conditionalFormatting sqref="G779 G782:G801">
     <cfRule type="cellIs" dxfId="47" priority="52" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G779 G782:G801">
+  <conditionalFormatting sqref="G803">
     <cfRule type="cellIs" dxfId="46" priority="51" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G803">
+  <conditionalFormatting sqref="G802">
     <cfRule type="cellIs" dxfId="45" priority="50" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G802">
+  <conditionalFormatting sqref="G258">
     <cfRule type="cellIs" dxfId="44" priority="49" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G258">
-    <cfRule type="cellIs" dxfId="43" priority="48" operator="equal">
+  <conditionalFormatting sqref="L849">
+    <cfRule type="cellIs" dxfId="43" priority="47" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L849">
+  <conditionalFormatting sqref="L848">
     <cfRule type="cellIs" dxfId="42" priority="46" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L848">
-    <cfRule type="cellIs" dxfId="41" priority="45" operator="equal">
+  <conditionalFormatting sqref="L851">
+    <cfRule type="cellIs" dxfId="41" priority="44" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L851">
+  <conditionalFormatting sqref="L850">
     <cfRule type="cellIs" dxfId="40" priority="43" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L850">
+  <conditionalFormatting sqref="L889">
     <cfRule type="cellIs" dxfId="39" priority="42" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L889">
+  <conditionalFormatting sqref="L888">
     <cfRule type="cellIs" dxfId="38" priority="41" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L888">
+  <conditionalFormatting sqref="L933">
     <cfRule type="cellIs" dxfId="37" priority="40" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L933">
+  <conditionalFormatting sqref="L932">
     <cfRule type="cellIs" dxfId="36" priority="39" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L932">
-    <cfRule type="cellIs" dxfId="35" priority="38" operator="equal">
+  <conditionalFormatting sqref="L882">
+    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L882">
+  <conditionalFormatting sqref="G850:G887 G890:G931 G933">
     <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G850:G887 G890:G931 G933">
-    <cfRule type="cellIs" dxfId="33" priority="35" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G602 L602">
-    <cfRule type="cellIs" dxfId="32" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G604:G605 L604:L605">
+    <cfRule type="cellIs" dxfId="32" priority="35" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G603 L603">
     <cfRule type="cellIs" dxfId="31" priority="34" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G603 L603">
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G609 L609">
-    <cfRule type="cellIs" dxfId="29" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G611:G613 G615:G619 L611:L613 L615:L619">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G610 L610">
     <cfRule type="cellIs" dxfId="28" priority="31" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G610 L610">
-    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G597 L597">
-    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G599:G600 L599:L600">
+    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G598 L598">
     <cfRule type="cellIs" dxfId="25" priority="28" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G598 L598">
-    <cfRule type="cellIs" dxfId="24" priority="27" operator="equal">
+  <conditionalFormatting sqref="G817">
+    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G817">
+  <conditionalFormatting sqref="G506">
     <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G506">
+  <conditionalFormatting sqref="F562">
     <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F562">
+  <conditionalFormatting sqref="L837">
     <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L837">
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G838 L838">
-    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G840:G841 L840:L841">
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G839 L839">
     <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G839 L839">
-    <cfRule type="cellIs" dxfId="17" priority="20" operator="equal">
-      <formula>"Fail"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G843 L843">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G845:G846 L845:L846">
+    <cfRule type="cellIs" dxfId="16" priority="19" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G844 L844">
     <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G844 L844">
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+  <conditionalFormatting sqref="G606:G607 L606:L607">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G606:G607 L606:L607">
+  <conditionalFormatting sqref="G639 L639">
     <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G639 L639">
+  <conditionalFormatting sqref="L934">
     <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L934">
+  <conditionalFormatting sqref="G934">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G934">
+  <conditionalFormatting sqref="L614">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L614">
+  <conditionalFormatting sqref="G220">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G220">
+  <conditionalFormatting sqref="G303">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G303">
+  <conditionalFormatting sqref="G192:G196 L193:L196">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G192:G196 L193:L196">
+  <conditionalFormatting sqref="L192">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L192">
+  <conditionalFormatting sqref="L191">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L191">
+  <conditionalFormatting sqref="G666 L666">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G666 L666">
+  <conditionalFormatting sqref="G675 L675">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G675 L675">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+  <conditionalFormatting sqref="G425">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G425">
+  <conditionalFormatting sqref="G426">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G426">
+  <conditionalFormatting sqref="K301:K303">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>

--- a/TAXI_ChecklistForAutoTestSTAXI.xlsx
+++ b/TAXI_ChecklistForAutoTestSTAXI.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4206" uniqueCount="2718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="2724">
   <si>
     <t>WEB STAXI - CHECKLIST AUTOMATION TEST</t>
   </si>
@@ -1331,7 +1331,7 @@
     <t>Popup Hiện trạng - Thời gian</t>
   </si>
   <si>
-    <t>Popup Hiện trạng: 18:24:47 13/04/26</t>
+    <t>Popup Hiện trạng: 08:32:30 15/04/26</t>
   </si>
   <si>
     <t>Minitor72</t>
@@ -1340,7 +1340,7 @@
     <t>Popup Hiện trạng - Tọa độ(Vĩ độ)</t>
   </si>
   <si>
-    <t>Popup Hiện trạng: 21.01937</t>
+    <t>Popup Hiện trạng: 21.02354</t>
   </si>
   <si>
     <t>Minitor73</t>
@@ -1349,7 +1349,7 @@
     <t>Popup Hiện trạng - Tọa độ(Kinh độ)</t>
   </si>
   <si>
-    <t>Popup Hiện trạng: 105.7925</t>
+    <t>Popup Hiện trạng: 105.8448</t>
   </si>
   <si>
     <t>Minitor74</t>
@@ -1358,7 +1358,7 @@
     <t>Popup Hiện trạng - Vị trí</t>
   </si>
   <si>
-    <t>Popup Hiện trạng: Trung Kính, P. Yên Hòa, TP. Hà Nội</t>
+    <t>Popup Hiện trạng: 65, Quán Sứ, P. Cửa Nam, TP. Hà Nội</t>
   </si>
   <si>
     <t>Minitor75</t>
@@ -1400,7 +1400,7 @@
     <t>Popup Hiện trạng - Cuốc khách</t>
   </si>
   <si>
-    <t>Popup Hiện trạng: 7 (TTĐH: 6; App: 0; Vẫy: 0)</t>
+    <t>Popup Hiện trạng: 0 (TTĐH: 0; App: 0; Vẫy: 0)</t>
   </si>
   <si>
     <t>Minitor80</t>
@@ -3816,33 +3816,19 @@
 2. Chọn button "Xuất excel" &gt; Check hiển thị</t>
   </si>
   <si>
-    <t>6.4.3 BC KM theo ngày</t>
-  </si>
-  <si>
     <t>Promotion38</t>
   </si>
   <si>
-    <t>Mở trang "BC KM theo ngày"</t>
-  </si>
-  <si>
-    <t>1. Login vào hệ thống
-2. Chọn chức năng "KHUYẾN MÃI" &gt; Báo cáo &gt; BC KM theo ngày &gt; Check hiển thị</t>
-  </si>
-  <si>
-    <t>Chuyển đến trang: "6.4.3 BC KM theo ngày"</t>
+    <t>6.4.3 BC KM theo thời gian</t>
   </si>
   <si>
     <t>Promotion39</t>
   </si>
   <si>
-    <t>1. Login vào hệ thống, tại trang "6.4.3 BC KM theo ngày" 
-2. Nhập các thông tin tìm kiếm:
-- Từ ngày: 10/12/2024 00:00
-- Đến ngày: 19/12/2024 23:59
-3. Tìm kiếm &gt; Check hiển thị</t>
-  </si>
-  <si>
-    <t>Hiển thị dữ liệu trong khoảng Từ ngày Đến ngày và hiển thị các trường: STT, Tên khuyến mại, Tổng tiền đã khuyến mại, Tổng số khuyến mại đã sử dụng.</t>
+    <t>Km cài app mới 4</t>
+  </si>
+  <si>
+    <t>Promotion39_BCKMTheoNgay_TimKiem.png</t>
   </si>
   <si>
     <t>Promotion40</t>
@@ -3852,6 +3838,11 @@
 2. Chọn button "Xuất excel" &gt; Check hiển thị</t>
   </si>
   <si>
+    <t>Dữ liệu web: 1
+Dữ liệu excel: Không có dữ liệu để xuất.
+ Dòng: A4</t>
+  </si>
+  <si>
     <t>6.4.4 BC KM theo tháng</t>
   </si>
   <si>
@@ -3866,6 +3857,9 @@
   </si>
   <si>
     <t>Chuyển đến trang: "6.4.4 BC KM theo tháng"</t>
+  </si>
+  <si>
+    <t>đã gộp vào báo cáo 6.4.3</t>
   </si>
   <si>
     <t>Promotion42</t>
@@ -4237,7 +4231,10 @@
  "Trần Hà Miên"</t>
   </si>
   <si>
-    <t>tr</t>
+    <t>Quang</t>
+  </si>
+  <si>
+    <t>Customer03_DanhSachKhachHang_TenHienThi.png</t>
   </si>
   <si>
     <t>Customer04</t>
@@ -10432,7 +10429,30 @@
     <t>Chuyển tới tab "Lịch sử", hiển thị trường: "Tác nhân"</t>
   </si>
   <si>
-    <t>đã gộp vào báo cáo 6.4.3</t>
+    <t>6.4.3 BC KM theo thời gian</t>
+  </si>
+  <si>
+    <t>1. Login vào hệ thống
+2. Chọn chức năng "KHUYẾN MÃI" &gt; Báo cáo &gt; BC KM theo thời gian &gt; Check hiển thị</t>
+  </si>
+  <si>
+    <t>1. Login vào hệ thống, tại trang "6.4.3 BC KM theo thời gian" 
+2. Nhập các thông tin tìm kiếm:
+- Từ ngày: 10/12/2024 00:00
+- Đến ngày: 19/12/2024 23:59
+3. Tìm kiếm &gt; Check hiển thị</t>
+  </si>
+  <si>
+    <t>Mở trang "BC KM theo thời gian"</t>
+  </si>
+  <si>
+    <t>Chuyển đến trang: "6.4.3 BC KM theo thời gian"</t>
+  </si>
+  <si>
+    <t>Hiển thị dữ liệu trong khoảng Từ ngày Đến ngày và hiển thị các trường: STT, Tên khuyến mại, Tổng tiền KM, ngày hoặc tháng</t>
+  </si>
+  <si>
+    <t>Hiện chỉ có báo cáo theo ngày</t>
   </si>
 </sst>
 </file>
@@ -10869,17 +10889,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10889,6 +10906,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -25429,8 +25449,8 @@
     <col min="13" max="13" width="20.42578125" style="21" customWidth="1"/>
     <col min="14" max="14" width="27.140625" style="21" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="79" customWidth="1"/>
-    <col min="16" max="3260" width="9.140625" style="79" customWidth="1"/>
-    <col min="3261" max="16384" width="9.140625" style="79"/>
+    <col min="16" max="3264" width="9.140625" style="79" customWidth="1"/>
+    <col min="3265" max="16384" width="9.140625" style="79"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -25450,13 +25470,13 @@
       <c r="L1" s="4"/>
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32"/>
@@ -25475,14 +25495,14 @@
       <c r="L2" s="4"/>
       <c r="M2" s="20"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="85"/>
+      <c r="V2" s="85"/>
     </row>
     <row r="3" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
@@ -25504,19 +25524,19 @@
       <c r="I3" s="80"/>
       <c r="J3" s="80"/>
       <c r="K3" s="80"/>
-      <c r="L3" s="88" t="s">
+      <c r="L3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="89"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
     </row>
     <row r="4" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32"/>
@@ -25529,11 +25549,11 @@
       </c>
       <c r="D4" s="15">
         <f>COUNTIFS(G:G,"Pass",H:H,"x")</f>
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E4" s="15">
         <f>COUNTIFS(G:G,"Fail",H:H,"x")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="6"/>
@@ -25544,18 +25564,18 @@
       <c r="L4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="87" t="s">
+      <c r="M4" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="85"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
     </row>
     <row r="5" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="32"/>
@@ -25583,18 +25603,18 @@
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="84" t="s">
+      <c r="M5" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="85"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
     </row>
     <row r="6" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32"/>
@@ -25622,10 +25642,10 @@
       <c r="L6" s="6">
         <v>2</v>
       </c>
-      <c r="M6" s="84" t="s">
+      <c r="M6" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="85"/>
+      <c r="N6" s="83"/>
       <c r="O6" s="81"/>
     </row>
     <row r="7" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -25639,11 +25659,11 @@
       </c>
       <c r="D7" s="15">
         <f>COUNTIFS(G:G,"Pass",K:K,"x")</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="15">
         <f>COUNTIFS(G:G,"Fail",K:K,"x")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="6"/>
@@ -25654,10 +25674,10 @@
       <c r="L7" s="6">
         <v>3</v>
       </c>
-      <c r="M7" s="84" t="s">
+      <c r="M7" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="85"/>
+      <c r="N7" s="83"/>
       <c r="O7" s="81"/>
     </row>
     <row r="8" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -33299,7 +33319,7 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="49" t="s">
-        <v>1024</v>
+        <v>2717</v>
       </c>
       <c r="B300" s="49"/>
       <c r="C300" s="50" t="s">
@@ -33319,20 +33339,24 @@
     </row>
     <row r="301" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="37" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B301" s="39" t="s">
-        <v>1026</v>
+        <v>2720</v>
       </c>
       <c r="C301" s="26"/>
       <c r="D301" s="62" t="s">
-        <v>1027</v>
+        <v>2718</v>
       </c>
       <c r="E301" s="27" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F301" s="29"/>
-      <c r="G301" s="4"/>
+        <v>2721</v>
+      </c>
+      <c r="F301" s="29" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G301" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="H301" s="6" t="s">
         <v>37</v>
       </c>
@@ -33341,24 +33365,30 @@
       <c r="K301" s="2"/>
       <c r="L301" s="2"/>
       <c r="M301" s="42"/>
-      <c r="N301" s="42"/>
+      <c r="N301" s="45" t="s">
+        <v>2723</v>
+      </c>
     </row>
     <row r="302" spans="1:14" ht="78.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="37" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B302" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C302" s="26"/>
       <c r="D302" s="62" t="s">
-        <v>1030</v>
+        <v>2719</v>
       </c>
       <c r="E302" s="29" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F302" s="29"/>
-      <c r="G302" s="4"/>
+        <v>2722</v>
+      </c>
+      <c r="F302" s="29" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G302" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="H302" s="6" t="s">
         <v>37</v>
       </c>
@@ -33366,25 +33396,33 @@
       <c r="J302" s="2"/>
       <c r="K302" s="2"/>
       <c r="L302" s="2"/>
-      <c r="M302" s="42"/>
-      <c r="N302" s="42"/>
+      <c r="M302" s="42" t="s">
+        <v>1028</v>
+      </c>
+      <c r="N302" s="45" t="s">
+        <v>2723</v>
+      </c>
     </row>
     <row r="303" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="37" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B303" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C303" s="26"/>
       <c r="D303" s="61" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E303" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="F303" s="29"/>
-      <c r="G303" s="4"/>
+      <c r="F303" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G303" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="H303" s="6" t="s">
         <v>37</v>
       </c>
@@ -33393,7 +33431,9 @@
       <c r="K303" s="2"/>
       <c r="L303" s="2"/>
       <c r="M303" s="42"/>
-      <c r="N303" s="42"/>
+      <c r="N303" s="45" t="s">
+        <v>2723</v>
+      </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B304" s="37"/>
@@ -33412,7 +33452,7 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="49" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B305" s="49"/>
       <c r="C305" s="50" t="s">
@@ -33432,17 +33472,17 @@
     </row>
     <row r="306" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="37" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B306" s="39" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C306" s="26"/>
       <c r="D306" s="62" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E306" s="27" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F306" s="29"/>
       <c r="G306" s="4"/>
@@ -33453,22 +33493,22 @@
       <c r="L306" s="2"/>
       <c r="M306" s="42"/>
       <c r="N306" s="45" t="s">
-        <v>2717</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="307" spans="1:14" ht="78.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="37" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B307" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C307" s="26"/>
       <c r="D307" s="62" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E307" s="29" t="s">
         <v>1040</v>
-      </c>
-      <c r="E307" s="29" t="s">
-        <v>1041</v>
       </c>
       <c r="F307" s="29"/>
       <c r="G307" s="4"/>
@@ -33479,19 +33519,19 @@
       <c r="L307" s="2"/>
       <c r="M307" s="42"/>
       <c r="N307" s="45" t="s">
-        <v>2717</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="308" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="37" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B308" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C308" s="26"/>
       <c r="D308" s="61" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E308" s="15" t="s">
         <v>153</v>
@@ -33505,7 +33545,7 @@
       <c r="L308" s="2"/>
       <c r="M308" s="42"/>
       <c r="N308" s="45" t="s">
-        <v>2717</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
@@ -33525,7 +33565,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="49" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B310" s="49"/>
       <c r="C310" s="50" t="s">
@@ -33545,17 +33585,17 @@
     </row>
     <row r="311" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="37" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B311" s="39" t="s">
         <v>1045</v>
-      </c>
-      <c r="B311" s="39" t="s">
-        <v>1046</v>
       </c>
       <c r="C311" s="26"/>
       <c r="D311" s="62" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E311" s="27" t="s">
         <v>1047</v>
-      </c>
-      <c r="E311" s="27" t="s">
-        <v>1048</v>
       </c>
       <c r="F311" s="29"/>
       <c r="G311" s="4"/>
@@ -33571,17 +33611,17 @@
     </row>
     <row r="312" spans="1:14" ht="78.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="37" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B312" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C312" s="26"/>
       <c r="D312" s="62" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E312" s="29" t="s">
         <v>1050</v>
-      </c>
-      <c r="E312" s="29" t="s">
-        <v>1051</v>
       </c>
       <c r="F312" s="29"/>
       <c r="G312" s="4"/>
@@ -33597,14 +33637,14 @@
     </row>
     <row r="313" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="37" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B313" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C313" s="26"/>
       <c r="D313" s="61" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E313" s="15" t="s">
         <v>153</v>
@@ -33638,7 +33678,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="49" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B315" s="49"/>
       <c r="C315" s="50" t="s">
@@ -33658,17 +33698,17 @@
     </row>
     <row r="316" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="37" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B316" s="39" t="s">
         <v>1055</v>
-      </c>
-      <c r="B316" s="39" t="s">
-        <v>1056</v>
       </c>
       <c r="C316" s="26"/>
       <c r="D316" s="62" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E316" s="27" t="s">
         <v>1057</v>
-      </c>
-      <c r="E316" s="27" t="s">
-        <v>1058</v>
       </c>
       <c r="F316" s="29"/>
       <c r="G316" s="4"/>
@@ -33684,17 +33724,17 @@
     </row>
     <row r="317" spans="1:14" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="37" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B317" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C317" s="26"/>
       <c r="D317" s="62" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E317" s="29" t="s">
         <v>1060</v>
-      </c>
-      <c r="E317" s="29" t="s">
-        <v>1061</v>
       </c>
       <c r="F317" s="29"/>
       <c r="G317" s="4"/>
@@ -33710,14 +33750,14 @@
     </row>
     <row r="318" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="37" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B318" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C318" s="26"/>
       <c r="D318" s="61" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E318" s="15" t="s">
         <v>153</v>
@@ -33752,7 +33792,7 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="49" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B320" s="49"/>
       <c r="C320" s="50" t="s">
@@ -33772,17 +33812,17 @@
     </row>
     <row r="321" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="37" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B321" s="39" t="s">
         <v>1065</v>
-      </c>
-      <c r="B321" s="39" t="s">
-        <v>1066</v>
       </c>
       <c r="C321" s="26"/>
       <c r="D321" s="62" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E321" s="27" t="s">
         <v>1067</v>
-      </c>
-      <c r="E321" s="27" t="s">
-        <v>1068</v>
       </c>
       <c r="F321" s="29"/>
       <c r="G321" s="4"/>
@@ -33798,17 +33838,17 @@
     </row>
     <row r="322" spans="1:14" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="37" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B322" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C322" s="26"/>
       <c r="D322" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E322" s="29" t="s">
         <v>1070</v>
-      </c>
-      <c r="E322" s="29" t="s">
-        <v>1071</v>
       </c>
       <c r="F322" s="29"/>
       <c r="G322" s="4"/>
@@ -33824,14 +33864,14 @@
     </row>
     <row r="323" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="37" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B323" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C323" s="26"/>
       <c r="D323" s="61" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E323" s="15" t="s">
         <v>153</v>
@@ -33866,7 +33906,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="49" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B325" s="49"/>
       <c r="C325" s="50" t="s">
@@ -33886,17 +33926,17 @@
     </row>
     <row r="326" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="37" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B326" s="39" t="s">
         <v>1075</v>
-      </c>
-      <c r="B326" s="39" t="s">
-        <v>1076</v>
       </c>
       <c r="C326" s="26"/>
       <c r="D326" s="62" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E326" s="27" t="s">
         <v>1077</v>
-      </c>
-      <c r="E326" s="27" t="s">
-        <v>1078</v>
       </c>
       <c r="F326" s="29"/>
       <c r="G326" s="4"/>
@@ -33912,17 +33952,17 @@
     </row>
     <row r="327" spans="1:14" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="37" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B327" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C327" s="26"/>
       <c r="D327" s="62" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E327" s="29" t="s">
         <v>1080</v>
-      </c>
-      <c r="E327" s="29" t="s">
-        <v>1081</v>
       </c>
       <c r="F327" s="29"/>
       <c r="G327" s="4"/>
@@ -33938,14 +33978,14 @@
     </row>
     <row r="328" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="37" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B328" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C328" s="26"/>
       <c r="D328" s="61" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E328" s="15" t="s">
         <v>153</v>
@@ -33980,7 +34020,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="49" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B330" s="49"/>
       <c r="C330" s="50" t="s">
@@ -34000,17 +34040,17 @@
     </row>
     <row r="331" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="37" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B331" s="39" t="s">
         <v>1085</v>
-      </c>
-      <c r="B331" s="39" t="s">
-        <v>1086</v>
       </c>
       <c r="C331" s="26"/>
       <c r="D331" s="62" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E331" s="27" t="s">
         <v>1087</v>
-      </c>
-      <c r="E331" s="27" t="s">
-        <v>1088</v>
       </c>
       <c r="F331" s="29"/>
       <c r="G331" s="4"/>
@@ -34026,17 +34066,17 @@
     </row>
     <row r="332" spans="1:14" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="37" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B332" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C332" s="26"/>
       <c r="D332" s="62" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E332" s="29" t="s">
         <v>1090</v>
-      </c>
-      <c r="E332" s="29" t="s">
-        <v>1091</v>
       </c>
       <c r="F332" s="29"/>
       <c r="G332" s="4"/>
@@ -34052,14 +34092,14 @@
     </row>
     <row r="333" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="37" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B333" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C333" s="26"/>
       <c r="D333" s="61" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E333" s="15" t="s">
         <v>153</v>
@@ -34094,7 +34134,7 @@
     </row>
     <row r="335" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="36" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B335" s="35"/>
       <c r="C335" s="18" t="s">
@@ -34114,20 +34154,20 @@
     </row>
     <row r="336" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="37" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B336" s="39" t="s">
         <v>930</v>
       </c>
       <c r="C336" s="26"/>
       <c r="D336" s="62" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E336" s="27" t="s">
         <v>1096</v>
       </c>
-      <c r="E336" s="27" t="s">
+      <c r="F336" s="15" t="s">
         <v>1097</v>
-      </c>
-      <c r="F336" s="15" t="s">
-        <v>1098</v>
       </c>
       <c r="G336" s="4" t="s">
         <v>4</v>
@@ -34146,17 +34186,17 @@
     </row>
     <row r="337" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="37" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B337" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C337" s="26"/>
       <c r="D337" s="62" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E337" s="29" t="s">
         <v>1100</v>
-      </c>
-      <c r="E337" s="29" t="s">
-        <v>1101</v>
       </c>
       <c r="F337" s="29"/>
       <c r="G337" s="4"/>
@@ -34172,17 +34212,17 @@
     </row>
     <row r="338" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="37" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B338" s="37" t="s">
         <v>485</v>
       </c>
       <c r="C338" s="26"/>
       <c r="D338" s="61" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E338" s="29" t="s">
         <v>1103</v>
-      </c>
-      <c r="E338" s="29" t="s">
-        <v>1104</v>
       </c>
       <c r="F338" s="29"/>
       <c r="G338" s="4"/>
@@ -34195,22 +34235,22 @@
       <c r="L338" s="2"/>
       <c r="M338" s="42"/>
       <c r="N338" s="42" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="339" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="37" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B339" s="37" t="s">
         <v>531</v>
       </c>
       <c r="C339" s="26"/>
       <c r="D339" s="61" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E339" s="29" t="s">
         <v>1107</v>
-      </c>
-      <c r="E339" s="29" t="s">
-        <v>1108</v>
       </c>
       <c r="F339" s="29"/>
       <c r="G339" s="4"/>
@@ -34242,7 +34282,7 @@
     </row>
     <row r="341" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="36" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B341" s="35"/>
       <c r="C341" s="18" t="s">
@@ -34262,20 +34302,20 @@
     </row>
     <row r="342" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="37" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B342" s="39" t="s">
         <v>1110</v>
-      </c>
-      <c r="B342" s="39" t="s">
-        <v>1111</v>
       </c>
       <c r="C342" s="26"/>
       <c r="D342" s="15" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E342" s="27" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F342" s="15" t="s">
         <v>1112</v>
-      </c>
-      <c r="F342" s="15" t="s">
-        <v>1113</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>4</v>
@@ -34294,17 +34334,17 @@
     </row>
     <row r="343" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="37" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B343" s="37" t="s">
         <v>1008</v>
       </c>
       <c r="C343" s="26"/>
       <c r="D343" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E343" s="29" t="s">
         <v>1115</v>
-      </c>
-      <c r="E343" s="29" t="s">
-        <v>1116</v>
       </c>
       <c r="F343" s="29"/>
       <c r="G343" s="4"/>
@@ -34320,17 +34360,17 @@
     </row>
     <row r="344" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="37" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B344" s="37" t="s">
         <v>485</v>
       </c>
       <c r="C344" s="26"/>
       <c r="D344" s="29" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E344" s="29" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F344" s="29"/>
       <c r="G344" s="4"/>
@@ -34343,22 +34383,22 @@
       <c r="L344" s="2"/>
       <c r="M344" s="42"/>
       <c r="N344" s="42" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="345" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="37" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B345" s="37" t="s">
         <v>531</v>
       </c>
       <c r="C345" s="26"/>
       <c r="D345" s="29" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E345" s="29" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F345" s="29"/>
       <c r="G345" s="4"/>
@@ -34390,7 +34430,7 @@
     </row>
     <row r="347" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="34" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B347" s="38"/>
       <c r="C347" s="17"/>
@@ -34408,7 +34448,7 @@
     </row>
     <row r="348" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="36" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B348" s="35"/>
       <c r="C348" s="18" t="s">
@@ -34428,20 +34468,20 @@
     </row>
     <row r="349" spans="1:14" ht="56.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="37" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B349" s="39" t="s">
         <v>1124</v>
-      </c>
-      <c r="B349" s="39" t="s">
-        <v>1125</v>
       </c>
       <c r="C349" s="26"/>
       <c r="D349" s="15" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E349" s="27" t="s">
         <v>1126</v>
       </c>
-      <c r="E349" s="27" t="s">
+      <c r="F349" s="15" t="s">
         <v>1127</v>
-      </c>
-      <c r="F349" s="15" t="s">
-        <v>1128</v>
       </c>
       <c r="G349" s="4" t="s">
         <v>4</v>
@@ -34460,17 +34500,17 @@
     </row>
     <row r="350" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B350" s="37" t="s">
         <v>417</v>
       </c>
       <c r="C350" s="26"/>
       <c r="D350" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E350" s="29" t="s">
         <v>1130</v>
-      </c>
-      <c r="E350" s="29" t="s">
-        <v>1131</v>
       </c>
       <c r="F350" s="29"/>
       <c r="G350" s="4"/>
@@ -34481,28 +34521,28 @@
       <c r="L350" s="2"/>
       <c r="M350" s="42"/>
       <c r="N350" s="45" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="351" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="37" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B351" s="37" t="s">
         <v>1133</v>
-      </c>
-      <c r="B351" s="37" t="s">
-        <v>1134</v>
       </c>
       <c r="C351" s="26"/>
       <c r="D351" s="15" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E351" s="29" t="s">
         <v>1135</v>
       </c>
-      <c r="E351" s="29" t="s">
+      <c r="F351" s="29" t="s">
         <v>1136</v>
       </c>
-      <c r="F351" s="29" t="s">
-        <v>1137</v>
-      </c>
       <c r="G351" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H351" s="2" t="s">
         <v>37</v>
@@ -34513,7 +34553,9 @@
         <v>37</v>
       </c>
       <c r="L351" s="2"/>
-      <c r="M351" s="42"/>
+      <c r="M351" s="42" t="s">
+        <v>1137</v>
+      </c>
       <c r="N351" s="42"/>
     </row>
     <row r="352" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
